--- a/IM/202604_Service_Count_Report.xlsx
+++ b/IM/202604_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$41</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="169">
   <si>
     <t>服務次數統計表        篩選月份：202604</t>
   </si>
@@ -173,6 +173,27 @@
     <t>士林</t>
   </si>
   <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>14:23:00</t>
+  </si>
+  <si>
+    <t>T301800079</t>
+  </si>
+  <si>
+    <t>eS-3018A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虹揚印刷股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號9樓之7</t>
+  </si>
+  <si>
+    <t>9F</t>
+  </si>
+  <si>
     <t>09:30:00</t>
   </si>
   <si>
@@ -182,9 +203,6 @@
     <t>T301800124</t>
   </si>
   <si>
-    <t>eS-3018A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">寶璽印刷有限公司 </t>
   </si>
   <si>
@@ -197,6 +215,24 @@
     <t>Pm</t>
   </si>
   <si>
+    <t>14:29:00</t>
+  </si>
+  <si>
+    <t>14:55:00</t>
+  </si>
+  <si>
+    <t>T302800122</t>
+  </si>
+  <si>
+    <t>eS-3028A 黑白複合機</t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號6樓</t>
+  </si>
+  <si>
+    <t>6F</t>
+  </si>
+  <si>
     <t>10:15:00</t>
   </si>
   <si>
@@ -206,9 +242,60 @@
     <t>eS-5015AC 彩色複合機</t>
   </si>
   <si>
+    <t>13:23:00</t>
+  </si>
+  <si>
+    <t>13:48:00</t>
+  </si>
+  <si>
+    <t>THILF04970</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區宜安路36、38號</t>
+  </si>
+  <si>
+    <t>中和一品苑</t>
+  </si>
+  <si>
+    <t>維修</t>
+  </si>
+  <si>
+    <t>軌道卡異物</t>
+  </si>
+  <si>
     <t>吳宗鴻</t>
   </si>
   <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>T301800172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">智基科技開發股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市淡水區中山路123號3樓(淡水分校)</t>
+  </si>
+  <si>
+    <t>淡水</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
+  </si>
+  <si>
     <t>10:30:00</t>
   </si>
   <si>
@@ -218,9 +305,6 @@
     <t>T302800006</t>
   </si>
   <si>
-    <t>eS-3028A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">信宇顧問有限公司 </t>
   </si>
   <si>
@@ -245,12 +329,6 @@
     <t>新北市淡水區中正路28號4樓(淡水)</t>
   </si>
   <si>
-    <t>淡水</t>
-  </si>
-  <si>
-    <t>PM抄表</t>
-  </si>
-  <si>
     <t>12:01:00</t>
   </si>
   <si>
@@ -260,6 +338,66 @@
     <t>送黑色碳粉 1</t>
   </si>
   <si>
+    <t>15:05:00</t>
+  </si>
+  <si>
+    <t>15:23:00</t>
+  </si>
+  <si>
+    <t>THILF02318</t>
+  </si>
+  <si>
+    <t>新北市淡水區北新路137、139號1F</t>
+  </si>
+  <si>
+    <t>北縣淡俊店</t>
+  </si>
+  <si>
+    <t>PMQ2 EDC</t>
+  </si>
+  <si>
+    <t>14:39:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>THILF02897</t>
+  </si>
+  <si>
+    <t>新北市淡水區北新路165.167號</t>
+  </si>
+  <si>
+    <t>淡水台電宿舍</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>THILF04658</t>
+  </si>
+  <si>
+    <t>新北市淡水區清水街2號、英專路43號</t>
+  </si>
+  <si>
+    <t>淡水英才店</t>
+  </si>
+  <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>THILF0A171</t>
+  </si>
+  <si>
+    <t>新北市淡水區水源街２段１９４號一樓及地下一樓全部</t>
+  </si>
+  <si>
+    <t>淡水金龍店</t>
+  </si>
+  <si>
     <t>湯家瑋</t>
   </si>
   <si>
@@ -302,25 +440,102 @@
     <t>4F</t>
   </si>
   <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>T351800045</t>
+  </si>
+  <si>
+    <t>eS-3518A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台灣善美的股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股生鮮物流)</t>
+  </si>
+  <si>
+    <t>五股生鮮物流</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>T352800029</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號4樓(五股)</t>
+  </si>
+  <si>
+    <t>五股4樓</t>
+  </si>
+  <si>
+    <t>T352800030</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股檢品)</t>
+  </si>
+  <si>
+    <t>五股檢品</t>
+  </si>
+  <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>T352800031</t>
+  </si>
+  <si>
+    <t>新北市五股區工商路128號1樓(五股DC廠工商運輸)</t>
+  </si>
+  <si>
+    <t>五股DC廠工商運輸</t>
+  </si>
+  <si>
+    <t>T352800032</t>
+  </si>
+  <si>
+    <t>新北市五股區五工六路35號1樓(五股運輸)</t>
+  </si>
+  <si>
+    <t>五股運輸</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>THILF03892</t>
+  </si>
+  <si>
+    <t>新北市蘆洲區光榮路68、70號一樓全部</t>
+  </si>
+  <si>
+    <t>蘆洲光榮店</t>
+  </si>
+  <si>
+    <t>更換發票機
+換上8155005389
+換下8155003126</t>
+  </si>
+  <si>
+    <t>16:20:00</t>
+  </si>
+  <si>
     <t>11:00:00</t>
   </si>
   <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
     <t>THILF03921</t>
   </si>
   <si>
-    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
-  </si>
-  <si>
     <t>新北市五股區五福路8、10號一樓全部</t>
   </si>
   <si>
     <t>五股福鑫店</t>
-  </si>
-  <si>
-    <t>PMQ2 EDC</t>
   </si>
   <si>
     <t>合計</t>
@@ -737,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1029,7 +1244,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2026040051</v>
+        <v>2026040130</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -1064,36 +1279,38 @@
       <c r="M5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="N5" s="8"/>
+      <c r="N5" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="O5" s="7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7">
-        <v>50227</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>287380</v>
+      </c>
+      <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
-      <c r="Z5" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026040052</v>
+        <v>2026040051</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1108,13 +1325,13 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>50</v>
@@ -1123,21 +1340,23 @@
         <v>36</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3">
         <v>50227</v>
       </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1145,7 +1364,7 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
@@ -1155,7 +1374,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026040053</v>
+        <v>2026040052</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1170,7 +1389,7 @@
         <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>55</v>
@@ -1179,31 +1398,27 @@
         <v>56</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="N7" s="8"/>
       <c r="O7" s="7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P7" s="7"/>
-      <c r="Q7" s="7">
-        <v>28637</v>
-      </c>
+      <c r="Q7" s="7"/>
       <c r="R7" s="7">
-        <v>718456</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>50227</v>
+      </c>
+      <c r="S7" s="7"/>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -1211,7 +1426,7 @@
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
@@ -1221,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026040054</v>
+        <v>2026040179</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1236,16 +1451,16 @@
         <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>36</v>
@@ -1254,18 +1469,18 @@
         <v>51</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="N8" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="O8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P8" s="3"/>
-      <c r="Q8" s="3">
-        <v>28637</v>
-      </c>
+      <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>718456</v>
+        <v>32628</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1275,17 +1490,21 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="7">
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026040055</v>
+        <v>2026040053</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1294,42 +1513,46 @@
         <v>29</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="7" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
+      <c r="Q9" s="7">
+        <v>28637</v>
+      </c>
       <c r="R9" s="7">
-        <v>34400</v>
-      </c>
-      <c r="S9" s="7"/>
+        <v>718456</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
@@ -1337,21 +1560,17 @@
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB9" s="7">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026040056</v>
+        <v>2026040054</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1360,48 +1579,44 @@
         <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N10" s="6"/>
       <c r="O10" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3">
-        <v>2879</v>
+        <v>28637</v>
       </c>
       <c r="R10" s="3">
-        <v>361051</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>718456</v>
+      </c>
+      <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1409,21 +1624,17 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="7">
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026040057</v>
+        <v>2026040104</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1432,44 +1643,42 @@
         <v>29</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="P11" s="7"/>
-      <c r="Q11" s="7">
-        <v>2879</v>
-      </c>
+      <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>361051</v>
+        <v>0</v>
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -1479,19 +1688,21 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AA11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB11" s="7"/>
+      <c r="AB11" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026040103</v>
+        <v>2026040108</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1500,56 +1711,54 @@
         <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3">
-        <v>2879</v>
-      </c>
+      <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>361051</v>
-      </c>
-      <c r="S12" s="3"/>
+        <v>27527</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T12" s="3"/>
-      <c r="U12" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="6" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>41</v>
@@ -1563,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026040033</v>
+        <v>2026040109</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -1572,48 +1781,44 @@
         <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P13" s="7"/>
-      <c r="Q13" s="7">
-        <v>377</v>
-      </c>
+      <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>3241</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>27527</v>
+      </c>
+      <c r="S13" s="7"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -1621,21 +1826,19 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB13" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB13" s="7"/>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026040034</v>
+        <v>2026040055</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1644,44 +1847,40 @@
         <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="N14" s="6"/>
       <c r="O14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="3"/>
-      <c r="Q14" s="3">
-        <v>377</v>
-      </c>
+      <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>3241</v>
+        <v>34400</v>
       </c>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -1691,19 +1890,21 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB14" s="3"/>
+      <c r="AB14" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="7">
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026040038</v>
+        <v>2026040057</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -1712,46 +1913,46 @@
         <v>29</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>86</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+      <c r="Q15" s="7">
+        <v>2879</v>
+      </c>
       <c r="R15" s="7">
-        <v>185800</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>361051</v>
+      </c>
+      <c r="S15" s="7"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -1759,7 +1960,7 @@
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
@@ -1773,7 +1974,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026040039</v>
+        <v>2026040056</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1782,44 +1983,48 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>86</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
+      <c r="Q16" s="3">
+        <v>2879</v>
+      </c>
       <c r="R16" s="3">
-        <v>185800</v>
-      </c>
-      <c r="S16" s="3"/>
+        <v>361051</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -1827,7 +2032,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>41</v>
@@ -1839,7 +2044,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026040040</v>
+        <v>2026040103</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -1848,54 +2053,56 @@
         <v>29</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
+      <c r="Q17" s="7">
+        <v>2879</v>
+      </c>
       <c r="R17" s="7">
-        <v>187678</v>
-      </c>
-      <c r="S17" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>361051</v>
+      </c>
+      <c r="S17" s="7"/>
       <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
+      <c r="U17" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
@@ -1909,7 +2116,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026040041</v>
+        <v>2026040161</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -1918,44 +2125,42 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>187678</v>
-      </c>
-      <c r="S18" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -1963,19 +2168,21 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="6" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB18" s="3"/>
+      <c r="AB18" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="7">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026040050</v>
+        <v>2026040157</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -1984,33 +2191,33 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
@@ -2021,17 +2228,13 @@
         <v>41</v>
       </c>
       <c r="T19" s="7"/>
-      <c r="U19" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U19" s="7"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
-      <c r="Y19" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>41</v>
@@ -2041,37 +2244,1447 @@
       </c>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB20" s="9">
-        <v>9</v>
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2026040111</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28">
+      <c r="A21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7">
+        <v>2026040123</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7">
+        <v>0</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2026040033</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3">
+        <v>377</v>
+      </c>
+      <c r="R22" s="3">
+        <v>3241</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" s="7">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7">
+        <v>2026040034</v>
+      </c>
+      <c r="C23" s="7">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7">
+        <v>377</v>
+      </c>
+      <c r="R23" s="7">
+        <v>3241</v>
+      </c>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB23" s="7"/>
+    </row>
+    <row r="24" spans="1:28">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2026040038</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3">
+        <v>185800</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28">
+      <c r="A25" s="7">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7">
+        <v>2026040039</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7">
+        <v>185800</v>
+      </c>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB25" s="7"/>
+    </row>
+    <row r="26" spans="1:28">
+      <c r="A26" s="3">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2026040040</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3">
+        <v>187678</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28">
+      <c r="A27" s="7">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7">
+        <v>2026040041</v>
+      </c>
+      <c r="C27" s="7">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7">
+        <v>187678</v>
+      </c>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB27" s="7"/>
+    </row>
+    <row r="28" spans="1:28">
+      <c r="A28" s="3">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2026040151</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3">
+        <v>120858</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+    </row>
+    <row r="29" spans="1:28">
+      <c r="A29" s="7">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7">
+        <v>2026040152</v>
+      </c>
+      <c r="C29" s="7">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7">
+        <v>120858</v>
+      </c>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB29" s="7"/>
+    </row>
+    <row r="30" spans="1:28">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2026040141</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3">
+        <v>16836</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+    </row>
+    <row r="31" spans="1:28">
+      <c r="A31" s="7">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7">
+        <v>2026040142</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7">
+        <v>16836</v>
+      </c>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB31" s="7"/>
+    </row>
+    <row r="32" spans="1:28">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2026040143</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3">
+        <v>69969</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+    </row>
+    <row r="33" spans="1:28">
+      <c r="A33" s="7">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7">
+        <v>2026040144</v>
+      </c>
+      <c r="C33" s="7">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7">
+        <v>69969</v>
+      </c>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB33" s="7"/>
+    </row>
+    <row r="34" spans="1:28">
+      <c r="A34" s="3">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2026040149</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3">
+        <v>155088</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+    </row>
+    <row r="35" spans="1:28">
+      <c r="A35" s="7">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7">
+        <v>2026040150</v>
+      </c>
+      <c r="C35" s="7">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7">
+        <v>155088</v>
+      </c>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB35" s="7"/>
+    </row>
+    <row r="36" spans="1:28">
+      <c r="A36" s="3">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3">
+        <v>2026040147</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3">
+        <v>116077</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+    </row>
+    <row r="37" spans="1:28">
+      <c r="A37" s="7">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7">
+        <v>2026040148</v>
+      </c>
+      <c r="C37" s="7">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7">
+        <v>116077</v>
+      </c>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB37" s="7"/>
+    </row>
+    <row r="38" spans="1:28">
+      <c r="A38" s="3">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3">
+        <v>2026040099</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3">
+        <v>0</v>
+      </c>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28">
+      <c r="A39" s="7">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7">
+        <v>2026040195</v>
+      </c>
+      <c r="C39" s="7">
+        <v>1</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7">
+        <v>0</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z39" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA39" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB39" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28">
+      <c r="A40" s="3">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2026040050</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3">
+        <v>0</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z40" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="10"/>
+      <c r="AA41" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB41" s="9">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202604_Service_Count_Report.xlsx
+++ b/IM/202604_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$75</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="253">
   <si>
     <t>服務次數統計表        篩選月份：202604</t>
   </si>
@@ -158,6 +158,21 @@
     <t>O</t>
   </si>
   <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>11:52:00</t>
+  </si>
+  <si>
+    <t>服務</t>
+  </si>
+  <si>
+    <t>Pm 網路改網段</t>
+  </si>
+  <si>
     <t>10:40:00</t>
   </si>
   <si>
@@ -173,6 +188,36 @@
     <t>士林</t>
   </si>
   <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>09:44:00</t>
+  </si>
+  <si>
+    <t>Pm</t>
+  </si>
+  <si>
+    <t>16:10:00</t>
+  </si>
+  <si>
+    <t>16:25:00</t>
+  </si>
+  <si>
+    <t>T301800018</t>
+  </si>
+  <si>
+    <t>eS-3018A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台灣大哥大股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區中正路790號10樓(中和中正10F)</t>
+  </si>
+  <si>
+    <t>中和中正10樓(黑)</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -182,9 +227,6 @@
     <t>T301800079</t>
   </si>
   <si>
-    <t>eS-3018A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">虹揚印刷股份有限公司 </t>
   </si>
   <si>
@@ -194,6 +236,12 @@
     <t>9F</t>
   </si>
   <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
     <t>09:30:00</t>
   </si>
   <si>
@@ -209,10 +257,25 @@
     <t>新北市中和區新民街112號5樓-7</t>
   </si>
   <si>
-    <t>服務</t>
-  </si>
-  <si>
-    <t>Pm</t>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>T302800020</t>
+  </si>
+  <si>
+    <t>eS-3028A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呈慈文理補習班 </t>
+  </si>
+  <si>
+    <t>新北市永和區保生路48巷5號1樓</t>
+  </si>
+  <si>
+    <t>全部紙夾調成厚紙模式</t>
   </si>
   <si>
     <t>14:29:00</t>
@@ -224,15 +287,33 @@
     <t>T302800122</t>
   </si>
   <si>
-    <t>eS-3028A 黑白複合機</t>
-  </si>
-  <si>
     <t>新北市中和區橋和路120號6樓</t>
   </si>
   <si>
     <t>6F</t>
   </si>
   <si>
+    <t>10:51:00</t>
+  </si>
+  <si>
+    <t>15:38:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>T352800007</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中康彩色印刷事業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建二路56號</t>
+  </si>
+  <si>
     <t>10:15:00</t>
   </si>
   <si>
@@ -272,9 +353,94 @@
     <t>軌道卡異物</t>
   </si>
   <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>12:24:00</t>
+  </si>
+  <si>
+    <t>THILF0C660</t>
+  </si>
+  <si>
+    <t>新北市中和區中和路414號</t>
+  </si>
+  <si>
+    <t>中和永安市場</t>
+  </si>
+  <si>
+    <t>PMQ2 EDC</t>
+  </si>
+  <si>
     <t>吳宗鴻</t>
   </si>
   <si>
+    <t>T252000025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">品興營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市泰山區莊田路與信華三街交叉口(華固一莊)</t>
+  </si>
+  <si>
+    <t>華固一莊</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
+  </si>
+  <si>
+    <t>14:11:00</t>
+  </si>
+  <si>
+    <t>T252000125</t>
+  </si>
+  <si>
+    <t>合作金庫商業銀行股份有限公司林口文化分行</t>
+  </si>
+  <si>
+    <t>新北市林口區文化二路1段62-5號2F(放款部</t>
+  </si>
+  <si>
+    <t>林口文化2F放款部</t>
+  </si>
+  <si>
+    <t>14:20:00</t>
+  </si>
+  <si>
+    <t>14:46:00</t>
+  </si>
+  <si>
+    <t>T252000153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">德森精密有限公司 </t>
+  </si>
+  <si>
+    <t>新北市林口區文化北路1段60巷108號3樓</t>
+  </si>
+  <si>
+    <t>PM抄表
+送黑色碳粉 1</t>
+  </si>
+  <si>
+    <t>11:25:00</t>
+  </si>
+  <si>
+    <t>11:47:00</t>
+  </si>
+  <si>
+    <t>T301800078</t>
+  </si>
+  <si>
+    <t>合作金庫商業銀行股份有限公司長庚分公司</t>
+  </si>
+  <si>
+    <t>桃園市龜山區復興街5號(林口長庚分行)</t>
+  </si>
+  <si>
+    <t>林口長庚分行</t>
+  </si>
+  <si>
     <t>12:15:00</t>
   </si>
   <si>
@@ -293,12 +459,6 @@
     <t>淡水</t>
   </si>
   <si>
-    <t>PM抄表</t>
-  </si>
-  <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
     <t>10:45:00</t>
   </si>
   <si>
@@ -311,6 +471,12 @@
     <t>新北市淡水區民族路50巷46號3樓</t>
   </si>
   <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>T302800131</t>
+  </si>
+  <si>
     <t>10:50:00</t>
   </si>
   <si>
@@ -338,6 +504,39 @@
     <t>送黑色碳粉 1</t>
   </si>
   <si>
+    <t>16:06:00</t>
+  </si>
+  <si>
+    <t>T352500149</t>
+  </si>
+  <si>
+    <t>eS-3525AC 彩色複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東南旅行社股份有限公司 </t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區忠孝東路17之3號(南崁分公司</t>
+  </si>
+  <si>
+    <t>南崁分公司</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>T452800047</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> eS-4528A 黑白複合機</t>
+  </si>
+  <si>
+    <t>新北市林口區文化二路1段62-5號1F(營業部)</t>
+  </si>
+  <si>
+    <t>林口文化1F營業部</t>
+  </si>
+  <si>
     <t>15:05:00</t>
   </si>
   <si>
@@ -353,9 +552,6 @@
     <t>北縣淡俊店</t>
   </si>
   <si>
-    <t>PMQ2 EDC</t>
-  </si>
-  <si>
     <t>14:39:00</t>
   </si>
   <si>
@@ -374,9 +570,6 @@
     <t>12:40:00</t>
   </si>
   <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
     <t>THILF04658</t>
   </si>
   <si>
@@ -416,6 +609,9 @@
     <t>pm</t>
   </si>
   <si>
+    <t>送發票</t>
+  </si>
+  <si>
     <t>10:00:00</t>
   </si>
   <si>
@@ -443,9 +639,6 @@
     <t>11:30:00</t>
   </si>
   <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
     <t>T351800045</t>
   </si>
   <si>
@@ -461,15 +654,30 @@
     <t>五股生鮮物流</t>
   </si>
   <si>
-    <t>13:30:00</t>
+    <t>T352500148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宏偉營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區光復路1段61巷26號2樓</t>
+  </si>
+  <si>
+    <t>T352800011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全聯實業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市蘆洲區水湳街74號2樓</t>
+  </si>
+  <si>
+    <t>蘆洲北二處</t>
   </si>
   <si>
     <t>T352800029</t>
   </si>
   <si>
-    <t>eS-3528A 黑白複合機</t>
-  </si>
-  <si>
     <t>新北市五股區五工六路35號4樓(五股)</t>
   </si>
   <si>
@@ -504,9 +712,6 @@
   </si>
   <si>
     <t>五股運輸</t>
-  </si>
-  <si>
-    <t>16:00:00</t>
   </si>
   <si>
     <t>THILF03892</t>
@@ -526,9 +731,6 @@
     <t>16:20:00</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
     <t>THILF03921</t>
   </si>
   <si>
@@ -536,6 +738,57 @@
   </si>
   <si>
     <t>五股福鑫店</t>
+  </si>
+  <si>
+    <t>THILF03929</t>
+  </si>
+  <si>
+    <t>新北市蘆洲區中山一路293/293-1號全部</t>
+  </si>
+  <si>
+    <t>蘆洲中山一</t>
+  </si>
+  <si>
+    <t>15:20:00</t>
+  </si>
+  <si>
+    <t>11:15:00</t>
+  </si>
+  <si>
+    <t>THILF0D193</t>
+  </si>
+  <si>
+    <t>新北市蘆洲區民權路113號</t>
+  </si>
+  <si>
+    <t>蘆洲權義店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">清潔校正 </t>
+  </si>
+  <si>
+    <t>狄澤洋</t>
+  </si>
+  <si>
+    <t>13:20:00</t>
+  </si>
+  <si>
+    <t>15:07:00</t>
+  </si>
+  <si>
+    <t>THILF04698</t>
+  </si>
+  <si>
+    <t>急修件</t>
+  </si>
+  <si>
+    <t>新北市三重區光復路二段117之1號</t>
+  </si>
+  <si>
+    <t>三重頂崁店</t>
+  </si>
+  <si>
+    <t>更換第一顆硬碟無備份還原</t>
   </si>
   <si>
     <t>合計</t>
@@ -952,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1176,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2026040100</v>
+        <v>2026040468</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1188,16 +1441,16 @@
         <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>35</v>
@@ -1209,29 +1462,33 @@
         <v>37</v>
       </c>
       <c r="M4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3">
-        <v>1813</v>
+        <v>4320</v>
       </c>
       <c r="R4" s="3">
-        <v>1352</v>
-      </c>
-      <c r="S4" s="3"/>
+        <v>17672</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="6"/>
+      <c r="Z4" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="AA4" s="3" t="s">
         <v>41</v>
       </c>
@@ -1244,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2026040130</v>
+        <v>2026040100</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -1268,27 +1525,29 @@
         <v>49</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
+      <c r="Q5" s="7">
+        <v>1813</v>
+      </c>
       <c r="R5" s="7">
-        <v>287380</v>
+        <v>1352</v>
       </c>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -1310,7 +1569,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026040051</v>
+        <v>2026040406</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1322,37 +1581,41 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="O6" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="Q6" s="3">
+        <v>1813</v>
+      </c>
       <c r="R6" s="3">
-        <v>50227</v>
+        <v>1360</v>
       </c>
       <c r="S6" s="3" t="s">
         <v>41</v>
@@ -1364,17 +1627,21 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026040052</v>
+        <v>2026040543</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1386,37 +1653,39 @@
         <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="8"/>
+        <v>60</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="O7" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7">
-        <v>50227</v>
+        <v>1492</v>
       </c>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -1425,18 +1694,20 @@
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
-      <c r="Z7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="7"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026040179</v>
+        <v>2026040130</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1451,28 +1722,28 @@
         <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>40</v>
@@ -1480,7 +1751,7 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>32628</v>
+        <v>287380</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1489,9 +1760,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="Z8" s="6"/>
       <c r="AA8" s="3" t="s">
         <v>41</v>
       </c>
@@ -1504,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026040053</v>
+        <v>2026040421</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1516,39 +1785,39 @@
         <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="8"/>
+        <v>66</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="O9" s="7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P9" s="7"/>
-      <c r="Q9" s="7">
-        <v>28637</v>
-      </c>
+      <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>718456</v>
+        <v>287382</v>
       </c>
       <c r="S9" s="7" t="s">
         <v>41</v>
@@ -1560,17 +1829,21 @@
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
+        <v>54</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026040054</v>
+        <v>2026040051</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1585,38 +1858,38 @@
         <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P10" s="3"/>
-      <c r="Q10" s="3">
-        <v>28637</v>
-      </c>
+      <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>718456</v>
-      </c>
-      <c r="S10" s="3"/>
+        <v>50227</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -1624,7 +1897,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
@@ -1634,7 +1907,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026040104</v>
+        <v>2026040052</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1658,27 +1931,25 @@
         <v>72</v>
       </c>
       <c r="J11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="M11" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>77</v>
-      </c>
+      <c r="N11" s="8"/>
       <c r="O11" s="7" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>0</v>
+        <v>50227</v>
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -1688,21 +1959,17 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB11" s="7">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026040108</v>
+        <v>2026040514</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1711,46 +1978,42 @@
         <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>27527</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>135975</v>
+      </c>
+      <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -1758,7 +2021,7 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>41</v>
@@ -1772,7 +2035,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026040109</v>
+        <v>2026040513</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -1781,44 +2044,44 @@
         <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>86</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="N13" s="8"/>
       <c r="O13" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>27527</v>
-      </c>
-      <c r="S13" s="7"/>
+        <v>135975</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -1826,11 +2089,9 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA13" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
     </row>
     <row r="14" spans="1:28">
@@ -1838,7 +2099,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026040055</v>
+        <v>2026040179</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1847,40 +2108,42 @@
         <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="N14" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="O14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>34400</v>
+        <v>32628</v>
       </c>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -1890,7 +2153,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
@@ -1904,7 +2167,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026040057</v>
+        <v>2026040424</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -1913,46 +2176,46 @@
         <v>29</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="N15" s="8" t="s">
         <v>86</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="7">
-        <v>2879</v>
-      </c>
+      <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>361051</v>
-      </c>
-      <c r="S15" s="7"/>
+        <v>32630</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -1960,7 +2223,7 @@
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="8" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
@@ -1974,7 +2237,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026040056</v>
+        <v>2026040539</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1983,44 +2246,40 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="N16" s="6"/>
       <c r="O16" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P16" s="3"/>
-      <c r="Q16" s="3">
-        <v>2879</v>
-      </c>
+      <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>361051</v>
+        <v>228034</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>41</v>
@@ -2032,19 +2291,21 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB16" s="3"/>
+      <c r="AB16" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="7">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026040103</v>
+        <v>2026040540</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2053,70 +2314,62 @@
         <v>29</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>86</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="N17" s="8"/>
       <c r="O17" s="7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P17" s="7"/>
-      <c r="Q17" s="7">
-        <v>2879</v>
-      </c>
+      <c r="Q17" s="7"/>
       <c r="R17" s="7">
-        <v>361051</v>
+        <v>228034</v>
       </c>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
-      <c r="U17" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U17" s="7"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB17" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB17" s="7"/>
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026040161</v>
+        <v>2026040053</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2125,38 +2378,42 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L18" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>106</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N18" s="6"/>
       <c r="O18" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
+      <c r="Q18" s="3">
+        <v>28637</v>
+      </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>718456</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>41</v>
@@ -2168,21 +2425,17 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="7">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026040157</v>
+        <v>2026040054</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2191,42 +2444,44 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
+        <v>95</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L19" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>112</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N19" s="8"/>
       <c r="O19" s="7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="Q19" s="7">
+        <v>28637</v>
+      </c>
       <c r="R19" s="7">
-        <v>0</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>718456</v>
+      </c>
+      <c r="S19" s="7"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -2234,21 +2489,17 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA19" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB19" s="7">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026040111</v>
+        <v>2026040104</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2257,42 +2508,44 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="L20" s="6" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
@@ -2300,7 +2553,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>41</v>
@@ -2314,7 +2567,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026040123</v>
+        <v>2026040470</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2323,33 +2576,33 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
@@ -2364,9 +2617,11 @@
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
+      <c r="Y21" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z21" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>41</v>
@@ -2380,7 +2635,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026040033</v>
+        <v>2026040422</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2389,19 +2644,19 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>35</v>
@@ -2410,23 +2665,25 @@
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="P22" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="P22" s="3">
+        <v>7643</v>
+      </c>
       <c r="Q22" s="3">
-        <v>377</v>
+        <v>16666</v>
       </c>
       <c r="R22" s="3">
-        <v>3241</v>
+        <v>23881</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>41</v>
@@ -2438,7 +2695,7 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>41</v>
@@ -2452,7 +2709,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026040034</v>
+        <v>2026040423</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2461,19 +2718,19 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>35</v>
@@ -2482,23 +2739,25 @@
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7">
+        <v>7643</v>
+      </c>
       <c r="Q23" s="7">
-        <v>377</v>
+        <v>16666</v>
       </c>
       <c r="R23" s="7">
-        <v>3241</v>
+        <v>23881</v>
       </c>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -2508,7 +2767,7 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="AA23" s="7" t="s">
         <v>41</v>
@@ -2520,7 +2779,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026040038</v>
+        <v>2026040488</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2529,46 +2788,46 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3">
+        <v>2082</v>
+      </c>
       <c r="R24" s="3">
-        <v>185800</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>105140</v>
+      </c>
+      <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -2576,21 +2835,17 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026040039</v>
+        <v>2026040487</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2599,44 +2854,48 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="Q25" s="7">
+        <v>2082</v>
+      </c>
       <c r="R25" s="7">
-        <v>185800</v>
-      </c>
-      <c r="S25" s="7"/>
+        <v>105140</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -2644,11 +2903,9 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA25" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
     </row>
     <row r="26" spans="1:28">
@@ -2656,7 +2913,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026040040</v>
+        <v>2026040498</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2665,54 +2922,56 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>135</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N26" s="6"/>
       <c r="O26" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="3">
+        <v>288</v>
+      </c>
       <c r="R26" s="3">
-        <v>187678</v>
+        <v>15686</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>41</v>
       </c>
       <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
+      <c r="U26" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>41</v>
@@ -2726,7 +2985,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026040041</v>
+        <v>2026040499</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -2735,42 +2994,42 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>135</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N27" s="8"/>
       <c r="O27" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
+      <c r="Q27" s="7">
+        <v>288</v>
+      </c>
       <c r="R27" s="7">
-        <v>187678</v>
+        <v>15686</v>
       </c>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -2780,7 +3039,7 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>41</v>
@@ -2792,7 +3051,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026040151</v>
+        <v>2026040465</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -2801,42 +3060,42 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3">
-        <v>120858</v>
+        <v>303520</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>41</v>
@@ -2848,7 +3107,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
@@ -2858,7 +3117,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026040152</v>
+        <v>2026040466</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -2867,34 +3126,34 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="O29" s="7" t="s">
         <v>40</v>
@@ -2902,7 +3161,7 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7">
-        <v>120858</v>
+        <v>303520</v>
       </c>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
@@ -2912,11 +3171,9 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA29" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
     </row>
     <row r="30" spans="1:28">
@@ -2924,7 +3181,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026040141</v>
+        <v>2026040108</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -2933,42 +3190,42 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="M30" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M30" s="6" t="s">
-        <v>146</v>
-      </c>
       <c r="N30" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3">
-        <v>16836</v>
+        <v>27527</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>41</v>
@@ -2980,17 +3237,21 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA30" s="3"/>
-      <c r="AB30" s="3"/>
+        <v>118</v>
+      </c>
+      <c r="AA30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="7">
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026040142</v>
+        <v>2026040109</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -2999,34 +3260,34 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="M31" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="M31" s="8" t="s">
-        <v>146</v>
-      </c>
       <c r="N31" s="8" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>40</v>
@@ -3034,7 +3295,7 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>16836</v>
+        <v>27527</v>
       </c>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
@@ -3044,7 +3305,7 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>41</v>
@@ -3056,7 +3317,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026040143</v>
+        <v>2026040055</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3065,46 +3326,42 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G32" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>150</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N32" s="6"/>
       <c r="O32" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3">
-        <v>69969</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>34400</v>
+      </c>
+      <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3112,17 +3369,21 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA32" s="3"/>
-      <c r="AB32" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026040144</v>
+        <v>2026040463</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3131,44 +3392,46 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>69969</v>
-      </c>
-      <c r="S33" s="7"/>
+        <v>92786</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -3176,11 +3439,9 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA33" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
@@ -3188,7 +3449,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026040149</v>
+        <v>2026040464</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3197,46 +3458,44 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>155088</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>92786</v>
+      </c>
+      <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -3244,7 +3503,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
@@ -3254,7 +3513,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026040150</v>
+        <v>2026040056</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3263,44 +3522,48 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G35" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="M35" s="8" t="s">
         <v>153</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
+      <c r="Q35" s="7">
+        <v>2879</v>
+      </c>
       <c r="R35" s="7">
-        <v>155088</v>
-      </c>
-      <c r="S35" s="7"/>
+        <v>361051</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -3308,19 +3571,21 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="AA35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="7"/>
+      <c r="AB35" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:28">
       <c r="A36" s="3">
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026040147</v>
+        <v>2026040057</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3329,46 +3594,46 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
+      <c r="Q36" s="3">
+        <v>2879</v>
+      </c>
       <c r="R36" s="3">
-        <v>116077</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>361051</v>
+      </c>
+      <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -3376,9 +3641,11 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA36" s="3"/>
+        <v>118</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
@@ -3386,7 +3653,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026040148</v>
+        <v>2026040103</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3395,64 +3662,70 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="H37" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
+      <c r="Q37" s="7">
+        <v>2879</v>
+      </c>
       <c r="R37" s="7">
-        <v>116077</v>
+        <v>361051</v>
       </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
+      <c r="U37" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="AA37" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB37" s="7"/>
+      <c r="AB37" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:28">
       <c r="A38" s="3">
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026040099</v>
+        <v>2026040537</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3461,44 +3734,48 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="K38" s="3" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
+      <c r="Q38" s="3">
+        <v>4501</v>
+      </c>
       <c r="R38" s="3">
-        <v>0</v>
-      </c>
-      <c r="S38" s="3"/>
+        <v>29387</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -3506,21 +3783,17 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB38" s="3">
-        <v>1</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="7">
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026040195</v>
+        <v>2026040538</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -3529,66 +3802,66 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="H39" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="I39" s="7" t="s">
+      <c r="J39" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
+      <c r="K39" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L39" s="8" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
+      <c r="Q39" s="7">
+        <v>4501</v>
+      </c>
       <c r="R39" s="7">
-        <v>0</v>
-      </c>
-      <c r="S39" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>29387</v>
+      </c>
+      <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
-      <c r="Y39" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AA39" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB39" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB39" s="7"/>
     </row>
     <row r="40" spans="1:28">
       <c r="A40" s="3">
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026040050</v>
+        <v>2026040485</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -3597,24 +3870,28 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L40" s="6" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>166</v>
@@ -3623,68 +3900,2346 @@
         <v>167</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>0</v>
+        <v>177932</v>
       </c>
       <c r="S40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="T40" s="3"/>
-      <c r="U40" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-      <c r="Y40" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="1:28">
+      <c r="A41" s="7">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7">
+        <v>2026040486</v>
+      </c>
+      <c r="C41" s="7">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7">
+        <v>177932</v>
+      </c>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
+    </row>
+    <row r="42" spans="1:28">
+      <c r="A42" s="3">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2026040161</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28">
+      <c r="A43" s="7">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7">
+        <v>2026040157</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7">
+        <v>0</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB43" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28">
+      <c r="A44" s="3">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2026040111</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28">
+      <c r="A45" s="7">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7">
+        <v>2026040123</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7">
+        <v>0</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA45" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB45" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28">
+      <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3">
+        <v>2026040033</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3">
+        <v>377</v>
+      </c>
+      <c r="R46" s="3">
+        <v>3241</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28">
+      <c r="A47" s="7">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7">
+        <v>2026040034</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7">
+        <v>377</v>
+      </c>
+      <c r="R47" s="7">
+        <v>3241</v>
+      </c>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA47" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB47" s="7"/>
+    </row>
+    <row r="48" spans="1:28">
+      <c r="A48" s="3">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3">
+        <v>2026040434</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3">
+        <v>377</v>
+      </c>
+      <c r="R48" s="3">
+        <v>3241</v>
+      </c>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z48" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28">
+      <c r="A49" s="7">
+        <v>47</v>
+      </c>
+      <c r="B49" s="7">
+        <v>2026040038</v>
+      </c>
+      <c r="C49" s="7">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="O49" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7">
+        <v>185800</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T49" s="7"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
+      <c r="Y49" s="7"/>
+      <c r="Z49" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA49" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB49" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28">
+      <c r="A50" s="3">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3">
+        <v>2026040039</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3">
+        <v>185800</v>
+      </c>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB50" s="3"/>
+    </row>
+    <row r="51" spans="1:28">
+      <c r="A51" s="7">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7">
+        <v>2026040040</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7">
+        <v>187678</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB51" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3">
+        <v>2026040041</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3">
+        <v>187678</v>
+      </c>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB52" s="3"/>
+    </row>
+    <row r="53" spans="1:28">
+      <c r="A53" s="7">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7">
+        <v>2026040151</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H53" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="AA40" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB40" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="10"/>
-      <c r="AA41" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB41" s="9">
-        <v>19</v>
+      <c r="I53" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7">
+        <v>120858</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA53" s="7"/>
+      <c r="AB53" s="7"/>
+    </row>
+    <row r="54" spans="1:28">
+      <c r="A54" s="3">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3">
+        <v>2026040152</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3">
+        <v>120858</v>
+      </c>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB54" s="3"/>
+    </row>
+    <row r="55" spans="1:28">
+      <c r="A55" s="7">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7">
+        <v>2026040439</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7">
+        <v>27727</v>
+      </c>
+      <c r="R55" s="7">
+        <v>47856</v>
+      </c>
+      <c r="S55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA55" s="7"/>
+      <c r="AB55" s="7"/>
+    </row>
+    <row r="56" spans="1:28">
+      <c r="A56" s="3">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3">
+        <v>2026040440</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3">
+        <v>27727</v>
+      </c>
+      <c r="R56" s="3">
+        <v>47856</v>
+      </c>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="1:28">
+      <c r="A57" s="7">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7">
+        <v>2026040481</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7">
+        <v>26583</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
+      <c r="Y57" s="7"/>
+      <c r="Z57" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA57" s="7"/>
+      <c r="AB57" s="7"/>
+    </row>
+    <row r="58" spans="1:28">
+      <c r="A58" s="3">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3">
+        <v>2026040482</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3">
+        <v>26583</v>
+      </c>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB58" s="3"/>
+    </row>
+    <row r="59" spans="1:28">
+      <c r="A59" s="7">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7">
+        <v>2026040141</v>
+      </c>
+      <c r="C59" s="7">
+        <v>1</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7">
+        <v>16836</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA59" s="7"/>
+      <c r="AB59" s="7"/>
+    </row>
+    <row r="60" spans="1:28">
+      <c r="A60" s="3">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3">
+        <v>2026040142</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3">
+        <v>16836</v>
+      </c>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB60" s="3"/>
+    </row>
+    <row r="61" spans="1:28">
+      <c r="A61" s="7">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7">
+        <v>2026040143</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7">
+        <v>69969</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA61" s="7"/>
+      <c r="AB61" s="7"/>
+    </row>
+    <row r="62" spans="1:28">
+      <c r="A62" s="3">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3">
+        <v>2026040144</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3">
+        <v>69969</v>
+      </c>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB62" s="3"/>
+    </row>
+    <row r="63" spans="1:28">
+      <c r="A63" s="7">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7">
+        <v>2026040149</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="N63" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="O63" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7">
+        <v>155088</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
+      <c r="Y63" s="7"/>
+      <c r="Z63" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA63" s="7"/>
+      <c r="AB63" s="7"/>
+    </row>
+    <row r="64" spans="1:28">
+      <c r="A64" s="3">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3">
+        <v>2026040150</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3">
+        <v>155088</v>
+      </c>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB64" s="3"/>
+    </row>
+    <row r="65" spans="1:28">
+      <c r="A65" s="7">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7">
+        <v>2026040147</v>
+      </c>
+      <c r="C65" s="7">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="N65" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="O65" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="7">
+        <v>116077</v>
+      </c>
+      <c r="S65" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T65" s="7"/>
+      <c r="U65" s="7"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="7"/>
+      <c r="X65" s="7"/>
+      <c r="Y65" s="7"/>
+      <c r="Z65" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA65" s="7"/>
+      <c r="AB65" s="7"/>
+    </row>
+    <row r="66" spans="1:28">
+      <c r="A66" s="3">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3">
+        <v>2026040148</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3">
+        <v>116077</v>
+      </c>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB66" s="3"/>
+    </row>
+    <row r="67" spans="1:28">
+      <c r="A67" s="7">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7">
+        <v>2026040099</v>
+      </c>
+      <c r="C67" s="7">
+        <v>1</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="N67" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="O67" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7">
+        <v>0</v>
+      </c>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA67" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB67" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28">
+      <c r="A68" s="3">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3">
+        <v>2026040195</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z68" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28">
+      <c r="A69" s="7">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7">
+        <v>2026040050</v>
+      </c>
+      <c r="C69" s="7">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="N69" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7">
+        <v>0</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T69" s="7"/>
+      <c r="U69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V69" s="7"/>
+      <c r="W69" s="7"/>
+      <c r="X69" s="7"/>
+      <c r="Y69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z69" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB69" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28">
+      <c r="A70" s="3">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3">
+        <v>2026040200</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA70" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28">
+      <c r="A71" s="7">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7">
+        <v>2026040511</v>
+      </c>
+      <c r="C71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="N71" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="O71" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7">
+        <v>0</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T71" s="7"/>
+      <c r="U71" s="7"/>
+      <c r="V71" s="7"/>
+      <c r="W71" s="7"/>
+      <c r="X71" s="7"/>
+      <c r="Y71" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z71" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA71" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB71" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28">
+      <c r="A72" s="3">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3">
+        <v>2026040469</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z72" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28">
+      <c r="A73" s="7">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7">
+        <v>2026040209</v>
+      </c>
+      <c r="C73" s="7">
+        <v>1</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="N73" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="O73" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="7">
+        <v>0</v>
+      </c>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="7"/>
+      <c r="W73" s="7"/>
+      <c r="X73" s="7"/>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA73" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB73" s="7"/>
+    </row>
+    <row r="74" spans="1:28">
+      <c r="A74" s="3">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3">
+        <v>2026040430</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA74" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28">
+      <c r="A75" s="9"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="9"/>
+      <c r="P75" s="9"/>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="9"/>
+      <c r="S75" s="9"/>
+      <c r="T75" s="9"/>
+      <c r="U75" s="9"/>
+      <c r="V75" s="9"/>
+      <c r="W75" s="9"/>
+      <c r="X75" s="9"/>
+      <c r="Y75" s="9"/>
+      <c r="Z75" s="10"/>
+      <c r="AA75" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202604_Service_Count_Report.xlsx
+++ b/IM/202604_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$118</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="365">
   <si>
     <t>服務次數統計表        篩選月份：202604</t>
   </si>
@@ -257,6 +257,24 @@
     <t>新北市中和區新民街112號5樓-7</t>
   </si>
   <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>T302800001</t>
+  </si>
+  <si>
+    <t>eS-3028A 黑白複合機</t>
+  </si>
+  <si>
+    <t>財團法人台北國際社區青年育樂活動中心基金會</t>
+  </si>
+  <si>
+    <t>台北市士林區天玉街26-1號</t>
+  </si>
+  <si>
+    <t>天玉街</t>
+  </si>
+  <si>
     <t>13:30:00</t>
   </si>
   <si>
@@ -266,9 +284,6 @@
     <t>T302800020</t>
   </si>
   <si>
-    <t>eS-3028A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">呈慈文理補習班 </t>
   </si>
   <si>
@@ -296,6 +311,45 @@
     <t>10:51:00</t>
   </si>
   <si>
+    <t>11:43:00</t>
+  </si>
+  <si>
+    <t>T351800121</t>
+  </si>
+  <si>
+    <t>eS-3518A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">羽田科技股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區中正路866-10號8樓</t>
+  </si>
+  <si>
+    <t>維修</t>
+  </si>
+  <si>
+    <t>清潔標籤紙殘雜 上熱待換</t>
+  </si>
+  <si>
+    <t>16:40:00</t>
+  </si>
+  <si>
+    <t>17:04:00</t>
+  </si>
+  <si>
+    <t>T352800006</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中原造像股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建康路130號7樓-11</t>
+  </si>
+  <si>
     <t>15:38:00</t>
   </si>
   <si>
@@ -305,9 +359,6 @@
     <t>T352800007</t>
   </si>
   <si>
-    <t>eS-3528A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">中康彩色印刷事業股份有限公司 </t>
   </si>
   <si>
@@ -323,6 +374,81 @@
     <t>eS-5015AC 彩色複合機</t>
   </si>
   <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>THILF02398</t>
+  </si>
+  <si>
+    <t>一般件</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區泰和街10號</t>
+  </si>
+  <si>
+    <t>中和泰和店</t>
+  </si>
+  <si>
+    <t>重拔網路線 測試正常</t>
+  </si>
+  <si>
+    <t>10:20:00</t>
+  </si>
+  <si>
+    <t>PMQ2 EDC</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>THILF03623</t>
+  </si>
+  <si>
+    <t>新北市三重區自強路二段74巷1號及特76號</t>
+  </si>
+  <si>
+    <t>三重自強店</t>
+  </si>
+  <si>
+    <t>裝潢回裝完工 已回報0800</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>PMQ1 7210002775</t>
+  </si>
+  <si>
+    <t>17:10:00</t>
+  </si>
+  <si>
+    <t>THILF04084</t>
+  </si>
+  <si>
+    <t>新北市三重區環河南路221巷14號及16號1樓全部</t>
+  </si>
+  <si>
+    <t>三重昌隆店</t>
+  </si>
+  <si>
+    <t>換下8183000467換上8183001862</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
     <t>13:23:00</t>
   </si>
   <si>
@@ -332,24 +458,12 @@
     <t>THILF04970</t>
   </si>
   <si>
-    <t>一般件</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t xml:space="preserve">萊爾富國際股份有限公司 </t>
-  </si>
-  <si>
     <t>新北市中和區宜安路36、38號</t>
   </si>
   <si>
     <t>中和一品苑</t>
   </si>
   <si>
-    <t>維修</t>
-  </si>
-  <si>
     <t>軌道卡異物</t>
   </si>
   <si>
@@ -368,7 +482,19 @@
     <t>中和永安市場</t>
   </si>
   <si>
-    <t>PMQ2 EDC</t>
+    <t>THILF0D350</t>
+  </si>
+  <si>
+    <t>新北市三重區三和路四段233號</t>
+  </si>
+  <si>
+    <t>三重徐匯站</t>
+  </si>
+  <si>
+    <t>10:06:00</t>
+  </si>
+  <si>
+    <t>重新整理排線 重新插拔客顯電源</t>
   </si>
   <si>
     <t>吳宗鴻</t>
@@ -471,12 +597,16 @@
     <t>新北市淡水區民族路50巷46號3樓</t>
   </si>
   <si>
-    <t>11:00:00</t>
-  </si>
-  <si>
     <t>T302800131</t>
   </si>
   <si>
+    <t>更換上熱
+滾筒
+滾筒刮片
+回收刮片
+鐵粉</t>
+  </si>
+  <si>
     <t>10:50:00</t>
   </si>
   <si>
@@ -555,9 +685,6 @@
     <t>14:39:00</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
     <t>THILF02897</t>
   </si>
   <si>
@@ -567,6 +694,42 @@
     <t>淡水台電宿舍</t>
   </si>
   <si>
+    <t>15:53:00</t>
+  </si>
+  <si>
+    <t>THILF03008</t>
+  </si>
+  <si>
+    <t>桃園市龜山區文化三路95,97號</t>
+  </si>
+  <si>
+    <t>龜山香品店</t>
+  </si>
+  <si>
+    <t>12:50:00</t>
+  </si>
+  <si>
+    <t>THILF04093</t>
+  </si>
+  <si>
+    <t>新北市淡水區新市一路一段104巷6號1樓</t>
+  </si>
+  <si>
+    <t>淡水新市一</t>
+  </si>
+  <si>
+    <t>13:20:00</t>
+  </si>
+  <si>
+    <t>THILF04153</t>
+  </si>
+  <si>
+    <t>新北市淡水區濱海路一段221號(金湯川溫泉汽旅區會館區一樓)</t>
+  </si>
+  <si>
+    <t>淡水莊園店</t>
+  </si>
+  <si>
     <t>12:40:00</t>
   </si>
   <si>
@@ -579,6 +742,32 @@
     <t>淡水英才店</t>
   </si>
   <si>
+    <t>整理清除異物髒污，重新啟動測試正常</t>
+  </si>
+  <si>
+    <t>11:07:00</t>
+  </si>
+  <si>
+    <t>更換掃描槍
+換下8119010513
+換上8119011505</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>12:10:00</t>
+  </si>
+  <si>
+    <t>THILF04802</t>
+  </si>
+  <si>
+    <t>新北市淡水區沙崙路214號</t>
+  </si>
+  <si>
+    <t>淡水沙崙店</t>
+  </si>
+  <si>
     <t>13:40:00</t>
   </si>
   <si>
@@ -591,9 +780,66 @@
     <t>淡水金龍店</t>
   </si>
   <si>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>15:12:00</t>
+  </si>
+  <si>
+    <t>THILF0L534</t>
+  </si>
+  <si>
+    <t>桃園市龜山區文興路30號</t>
+  </si>
+  <si>
+    <t>田倉文興店</t>
+  </si>
+  <si>
+    <t>PMQ2</t>
+  </si>
+  <si>
     <t>湯家瑋</t>
   </si>
   <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>T252000086</t>
+  </si>
+  <si>
+    <t>新北市三重區仁義街79巷旁工地</t>
+  </si>
+  <si>
+    <t>華固慕川</t>
+  </si>
+  <si>
+    <t>pm</t>
+  </si>
+  <si>
+    <t>T252000102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仲誠不動產經紀有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區重新路3段110號</t>
+  </si>
+  <si>
+    <t>三重</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>T252000113</t>
+  </si>
+  <si>
+    <t>新北市三重區仁義街與元信一街交叉口</t>
+  </si>
+  <si>
+    <t>華固織幸</t>
+  </si>
+  <si>
     <t>09:00:00</t>
   </si>
   <si>
@@ -603,16 +849,25 @@
     <t>新北市三重區德厚街76號7樓</t>
   </si>
   <si>
-    <t>三重</t>
-  </si>
-  <si>
-    <t>pm</t>
-  </si>
-  <si>
     <t>送發票</t>
   </si>
   <si>
-    <t>10:00:00</t>
+    <t>T301800171</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正區336-1號(新莊)</t>
+  </si>
+  <si>
+    <t>新莊</t>
+  </si>
+  <si>
+    <t>T301800174</t>
+  </si>
+  <si>
+    <t>新北市板橋區中山路1段10號5樓(板橋分校)</t>
+  </si>
+  <si>
+    <t>板橋</t>
   </si>
   <si>
     <t>T302800007</t>
@@ -636,13 +891,25 @@
     <t>4F</t>
   </si>
   <si>
+    <t>T302800012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">捷旺宅不動產經紀有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區捷運路32號</t>
+  </si>
+  <si>
+    <t>T302800123</t>
+  </si>
+  <si>
+    <t>新北市三重區正義北路218號(三重分校)</t>
+  </si>
+  <si>
     <t>11:30:00</t>
   </si>
   <si>
     <t>T351800045</t>
-  </si>
-  <si>
-    <t>eS-3518A 黑白複合機</t>
   </si>
   <si>
     <t xml:space="preserve">台灣善美的股份有限公司 </t>
@@ -752,6 +1019,53 @@
     <t>15:20:00</t>
   </si>
   <si>
+    <t>THILF04025</t>
+  </si>
+  <si>
+    <t>新北市新莊區中信街20號一樓全部、22號一樓部份</t>
+  </si>
+  <si>
+    <t>新莊祐信店</t>
+  </si>
+  <si>
+    <t>裝潢設備已收回</t>
+  </si>
+  <si>
+    <t>撤店</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>THILF05057</t>
+  </si>
+  <si>
+    <t>急修件</t>
+  </si>
+  <si>
+    <t>新北市新莊區中港路84號1樓</t>
+  </si>
+  <si>
+    <t>新莊中港店</t>
+  </si>
+  <si>
+    <t>電源脫落 重接電源 重設HUB</t>
+  </si>
+  <si>
+    <t>THILF0D174</t>
+  </si>
+  <si>
+    <t>新北市新莊區裕民街83之6號</t>
+  </si>
+  <si>
+    <t>新莊裕民店</t>
+  </si>
+  <si>
+    <t>更換發票機
+換上8155005451
+換下8155002911</t>
+  </si>
+  <si>
     <t>11:15:00</t>
   </si>
   <si>
@@ -767,21 +1081,36 @@
     <t xml:space="preserve">清潔校正 </t>
   </si>
   <si>
+    <t>TX81000005</t>
+  </si>
+  <si>
+    <t>TCx810 POS 終端系統</t>
+  </si>
+  <si>
+    <t>POS商品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日商樂比亞股份有限公司台灣分公司 </t>
+  </si>
+  <si>
+    <t>新北市新莊區新北大道4段3號B2</t>
+  </si>
+  <si>
+    <t>新莊宏匯店</t>
+  </si>
+  <si>
+    <t>立式掃描器喇叭異常帶回檢修</t>
+  </si>
+  <si>
     <t>狄澤洋</t>
   </si>
   <si>
-    <t>13:20:00</t>
-  </si>
-  <si>
     <t>15:07:00</t>
   </si>
   <si>
     <t>THILF04698</t>
   </si>
   <si>
-    <t>急修件</t>
-  </si>
-  <si>
     <t>新北市三重區光復路二段117之1號</t>
   </si>
   <si>
@@ -789,6 +1118,23 @@
   </si>
   <si>
     <t>更換第一顆硬碟無備份還原</t>
+  </si>
+  <si>
+    <t>THILF0D111</t>
+  </si>
+  <si>
+    <t>新北市板橋區府中路24號</t>
+  </si>
+  <si>
+    <t>板橋府中店</t>
+  </si>
+  <si>
+    <t>更換T70
+換上 8138001526
+換下 8138001580</t>
+  </si>
+  <si>
+    <t>12:28:00</t>
   </si>
   <si>
     <t>合計</t>
@@ -1205,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AB118"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1969,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026040514</v>
+        <v>2026040913</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1981,37 +2327,39 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="N12" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N12" s="6"/>
       <c r="O12" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>135975</v>
+        <v>80502</v>
       </c>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -2020,9 +2368,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-      <c r="Z12" s="6" t="s">
-        <v>81</v>
-      </c>
+      <c r="Z12" s="6"/>
       <c r="AA12" s="3" t="s">
         <v>41</v>
       </c>
@@ -2050,25 +2396,25 @@
         <v>42</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N13" s="8"/>
       <c r="O13" s="7" t="s">
@@ -2089,7 +2435,7 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
@@ -2099,7 +2445,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026040179</v>
+        <v>2026040514</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2111,39 +2457,37 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="N14" s="6" t="s">
-        <v>86</v>
-      </c>
+      <c r="N14" s="6"/>
       <c r="O14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>32628</v>
+        <v>135975</v>
       </c>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -2153,21 +2497,19 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="6" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB14" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB14" s="3"/>
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="7">
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026040424</v>
+        <v>2026040179</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2179,19 +2521,19 @@
         <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
@@ -2200,22 +2542,20 @@
         <v>65</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>32630</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>32628</v>
+      </c>
+      <c r="S15" s="7"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -2237,7 +2577,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026040539</v>
+        <v>2026040424</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2252,34 +2592,36 @@
         <v>42</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="N16" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="O16" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>228034</v>
+        <v>32630</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>41</v>
@@ -2305,7 +2647,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026040540</v>
+        <v>2026040899</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2317,37 +2659,37 @@
         <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N17" s="8"/>
       <c r="O17" s="7" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7">
-        <v>228034</v>
+        <v>70987</v>
       </c>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -2357,19 +2699,21 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB17" s="7"/>
+      <c r="AB17" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026040053</v>
+        <v>2026040555</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2381,39 +2725,37 @@
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3">
-        <v>28637</v>
-      </c>
+      <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>718456</v>
+        <v>127085</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>41</v>
@@ -2427,15 +2769,19 @@
       <c r="Z18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
+      <c r="AA18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="7">
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026040054</v>
+        <v>2026040556</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2447,39 +2793,37 @@
         <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P19" s="7"/>
-      <c r="Q19" s="7">
-        <v>28637</v>
-      </c>
+      <c r="Q19" s="7"/>
       <c r="R19" s="7">
-        <v>718456</v>
+        <v>127085</v>
       </c>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -2491,7 +2835,9 @@
       <c r="Z19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="AA19" s="7"/>
+      <c r="AA19" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB19" s="7"/>
     </row>
     <row r="20" spans="1:28">
@@ -2499,7 +2845,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026040104</v>
+        <v>2026040539</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2511,41 +2857,41 @@
         <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>104</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N20" s="6"/>
       <c r="O20" s="3" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3"/>
+        <v>228034</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
@@ -2553,7 +2899,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="6" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>41</v>
@@ -2567,7 +2913,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026040470</v>
+        <v>2026040540</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2582,60 +2928,56 @@
         <v>42</v>
       </c>
       <c r="G21" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="I21" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="J21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="N21" s="8" t="s">
-        <v>111</v>
-      </c>
+      <c r="N21" s="8"/>
       <c r="O21" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7">
-        <v>0</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>228034</v>
+      </c>
+      <c r="S21" s="7"/>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="Y21" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB21" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB21" s="7"/>
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="3">
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026040422</v>
+        <v>2026040053</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2644,46 +2986,42 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>117</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N22" s="6"/>
       <c r="O22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="P22" s="3">
-        <v>7643</v>
-      </c>
+      <c r="P22" s="3"/>
       <c r="Q22" s="3">
-        <v>16666</v>
+        <v>28637</v>
       </c>
       <c r="R22" s="3">
-        <v>23881</v>
+        <v>718456</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>41</v>
@@ -2695,21 +3033,17 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026040423</v>
+        <v>2026040054</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2718,46 +3052,42 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>117</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P23" s="7">
-        <v>7643</v>
-      </c>
+      <c r="P23" s="7"/>
       <c r="Q23" s="7">
-        <v>16666</v>
+        <v>28637</v>
       </c>
       <c r="R23" s="7">
-        <v>23881</v>
+        <v>718456</v>
       </c>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -2767,11 +3097,9 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA23" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA23" s="7"/>
       <c r="AB23" s="7"/>
     </row>
     <row r="24" spans="1:28">
@@ -2779,7 +3107,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026040488</v>
+        <v>2026040578</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2788,44 +3116,42 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="N24" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="O24" s="3" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3">
-        <v>2082</v>
-      </c>
+      <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>105140</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -2835,17 +3161,21 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026040487</v>
+        <v>2026041011</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2854,44 +3184,38 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="H25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="N25" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>123</v>
       </c>
       <c r="O25" s="7" t="s">
         <v>45</v>
       </c>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7">
-        <v>2082</v>
-      </c>
+      <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>105140</v>
+        <v>0</v>
       </c>
       <c r="S25" s="7" t="s">
         <v>41</v>
@@ -2901,11 +3225,15 @@
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
+      <c r="Y25" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA25" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB25" s="7"/>
     </row>
     <row r="26" spans="1:28">
@@ -2913,7 +3241,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026040498</v>
+        <v>2026040820</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2922,56 +3250,50 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
       <c r="L26" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="N26" s="6"/>
+      <c r="N26" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="O26" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3">
-        <v>288</v>
-      </c>
+      <c r="Q26" s="3"/>
       <c r="R26" s="3">
-        <v>15686</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>41</v>
@@ -2985,7 +3307,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026040499</v>
+        <v>2026040819</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -2994,64 +3316,66 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M27" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="N27" s="8"/>
+      <c r="N27" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="O27" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7">
-        <v>288</v>
-      </c>
+      <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>15686</v>
-      </c>
-      <c r="S27" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
+      <c r="Y27" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z27" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB27" s="7"/>
+      <c r="AB27" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="3">
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026040465</v>
+        <v>2026040591</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3060,46 +3384,44 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3">
-        <v>303520</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -3107,17 +3429,21 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026040466</v>
+        <v>2026040881</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3126,54 +3452,56 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7">
-        <v>303520</v>
-      </c>
-      <c r="S29" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
+      <c r="Y29" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z29" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA29" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA29" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB29" s="7"/>
     </row>
     <row r="30" spans="1:28">
@@ -3181,7 +3509,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026040108</v>
+        <v>2026040104</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3190,46 +3518,44 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3">
-        <v>27527</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -3237,7 +3563,7 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="AA30" s="3" t="s">
         <v>41</v>
@@ -3251,7 +3577,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026040109</v>
+        <v>2026040470</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3260,64 +3586,66 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
       <c r="L31" s="8" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>27527</v>
-      </c>
-      <c r="S31" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
+      <c r="Y31" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z31" s="8" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB31" s="7"/>
+      <c r="AB31" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:28">
       <c r="A32" s="3">
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026040055</v>
+        <v>2026040627</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3326,50 +3654,52 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
       <c r="L32" s="6" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="N32" s="6"/>
+        <v>151</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>152</v>
+      </c>
       <c r="O32" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3">
-        <v>34400</v>
-      </c>
-      <c r="S32" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
+      <c r="Y32" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z32" s="6" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>41</v>
@@ -3383,7 +3713,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026040463</v>
+        <v>2026040565</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3392,46 +3722,44 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>92786</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -3439,9 +3767,11 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA33" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="AA33" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
@@ -3449,7 +3779,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026040464</v>
+        <v>2026040422</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3458,44 +3788,50 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="P34" s="3">
+        <v>7643</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>16666</v>
+      </c>
       <c r="R34" s="3">
-        <v>92786</v>
-      </c>
-      <c r="S34" s="3"/>
+        <v>23881</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -3503,17 +3839,21 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA34" s="3"/>
-      <c r="AB34" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="AA34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:28">
       <c r="A35" s="7">
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026040056</v>
+        <v>2026040423</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3522,48 +3862,48 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>149</v>
+        <v>47</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="P35" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="P35" s="7">
+        <v>7643</v>
+      </c>
       <c r="Q35" s="7">
-        <v>2879</v>
+        <v>16666</v>
       </c>
       <c r="R35" s="7">
-        <v>361051</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>23881</v>
+      </c>
+      <c r="S35" s="7"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -3571,21 +3911,19 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="AA35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
       <c r="A36" s="3">
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026040057</v>
+        <v>2026040487</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3594,46 +3932,48 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3">
-        <v>2879</v>
+        <v>2082</v>
       </c>
       <c r="R36" s="3">
-        <v>361051</v>
-      </c>
-      <c r="S36" s="3"/>
+        <v>105140</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -3641,11 +3981,9 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA36" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
@@ -3653,7 +3991,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026040103</v>
+        <v>2026040488</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3662,70 +4000,64 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7">
-        <v>2879</v>
+        <v>2082</v>
       </c>
       <c r="R37" s="7">
-        <v>361051</v>
+        <v>105140</v>
       </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
-      <c r="U37" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA37" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB37" s="7">
-        <v>1</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:28">
       <c r="A38" s="3">
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026040537</v>
+        <v>2026040498</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3734,66 +4066,70 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>162</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N38" s="6"/>
       <c r="O38" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3">
-        <v>4501</v>
+        <v>288</v>
       </c>
       <c r="R38" s="3">
-        <v>29387</v>
+        <v>15686</v>
       </c>
       <c r="S38" s="3" t="s">
         <v>41</v>
       </c>
       <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
+      <c r="U38" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA38" s="3"/>
-      <c r="AB38" s="3"/>
+        <v>171</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="7">
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026040538</v>
+        <v>2026040499</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -3802,44 +4138,42 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>162</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N39" s="8"/>
       <c r="O39" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P39" s="7"/>
       <c r="Q39" s="7">
-        <v>4501</v>
+        <v>288</v>
       </c>
       <c r="R39" s="7">
-        <v>29387</v>
+        <v>15686</v>
       </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
@@ -3849,7 +4183,7 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="AA39" s="7" t="s">
         <v>41</v>
@@ -3861,7 +4195,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026040485</v>
+        <v>2026040465</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -3870,34 +4204,34 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>45</v>
@@ -3905,7 +4239,7 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>177932</v>
+        <v>303520</v>
       </c>
       <c r="S40" s="3" t="s">
         <v>41</v>
@@ -3917,7 +4251,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
@@ -3927,7 +4261,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026040486</v>
+        <v>2026040466</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -3936,34 +4270,34 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="O41" s="7" t="s">
         <v>40</v>
@@ -3971,7 +4305,7 @@
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7">
-        <v>177932</v>
+        <v>303520</v>
       </c>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
@@ -3981,7 +4315,7 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="AA41" s="7"/>
       <c r="AB41" s="7"/>
@@ -3991,7 +4325,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026040161</v>
+        <v>2026040108</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4000,30 +4334,34 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L42" s="6" t="s">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>45</v>
@@ -4031,7 +4369,7 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3">
-        <v>0</v>
+        <v>27527</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>41</v>
@@ -4043,7 +4381,7 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>41</v>
@@ -4057,7 +4395,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026040157</v>
+        <v>2026040109</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4066,42 +4404,44 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
+        <v>180</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L43" s="8" t="s">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>0</v>
-      </c>
-      <c r="S43" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>27527</v>
+      </c>
+      <c r="S43" s="7"/>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
@@ -4109,21 +4449,19 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="AA43" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB43" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB43" s="7"/>
     </row>
     <row r="44" spans="1:28">
       <c r="A44" s="3">
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026040111</v>
+        <v>2026040055</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4132,42 +4470,42 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>178</v>
+        <v>69</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
+        <v>185</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L44" s="6" t="s">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>181</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N44" s="6"/>
       <c r="O44" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>34400</v>
+      </c>
+      <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
@@ -4175,7 +4513,7 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="AA44" s="3" t="s">
         <v>41</v>
@@ -4189,7 +4527,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026040123</v>
+        <v>2026040463</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4198,30 +4536,34 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
+        <v>188</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L45" s="8" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>45</v>
@@ -4229,7 +4571,7 @@
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>0</v>
+        <v>92786</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>41</v>
@@ -4241,21 +4583,17 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA45" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB45" s="7">
-        <v>1</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AA45" s="7"/>
+      <c r="AB45" s="7"/>
     </row>
     <row r="46" spans="1:28">
       <c r="A46" s="3">
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026040033</v>
+        <v>2026040464</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4264,48 +4602,44 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>188</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P46" s="3"/>
-      <c r="Q46" s="3">
-        <v>377</v>
-      </c>
+      <c r="Q46" s="3"/>
       <c r="R46" s="3">
-        <v>3241</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>92786</v>
+      </c>
+      <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
@@ -4313,21 +4647,17 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>1</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
     </row>
     <row r="47" spans="1:28">
       <c r="A47" s="7">
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026040034</v>
+        <v>2026040791</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4336,44 +4666,42 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>187</v>
+        <v>69</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>188</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P47" s="7"/>
-      <c r="Q47" s="7">
-        <v>377</v>
-      </c>
+      <c r="Q47" s="7"/>
       <c r="R47" s="7">
-        <v>3241</v>
+        <v>92786</v>
       </c>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
@@ -4381,21 +4709,25 @@
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
-      <c r="Y47" s="7"/>
+      <c r="Y47" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z47" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AA47" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB47" s="7"/>
+      <c r="AB47" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:28">
       <c r="A48" s="3">
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026040434</v>
+        <v>2026040056</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4404,58 +4736,56 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3">
-        <v>377</v>
+        <v>2879</v>
       </c>
       <c r="R48" s="3">
-        <v>3241</v>
-      </c>
-      <c r="S48" s="3"/>
+        <v>361051</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
-      <c r="W48" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="W48" s="3"/>
       <c r="X48" s="3"/>
-      <c r="Y48" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>41</v>
@@ -4469,7 +4799,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026040038</v>
+        <v>2026040057</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4478,46 +4808,46 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="H49" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="J49" s="7" t="s">
         <v>193</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="M49" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="N49" s="8" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="7">
+        <v>2879</v>
+      </c>
       <c r="R49" s="7">
-        <v>185800</v>
-      </c>
-      <c r="S49" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>361051</v>
+      </c>
+      <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
@@ -4525,21 +4855,19 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB49" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB49" s="7"/>
     </row>
     <row r="50" spans="1:28">
       <c r="A50" s="3">
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026040039</v>
+        <v>2026040103</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4548,64 +4876,70 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>70</v>
+        <v>196</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="M50" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="M50" s="6" t="s">
-        <v>196</v>
-      </c>
       <c r="N50" s="6" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
+      <c r="Q50" s="3">
+        <v>2879</v>
+      </c>
       <c r="R50" s="3">
-        <v>185800</v>
+        <v>361051</v>
       </c>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
+      <c r="U50" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AA50" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB50" s="3"/>
+      <c r="AB50" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:28">
       <c r="A51" s="7">
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026040040</v>
+        <v>2026040538</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4614,46 +4948,46 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
+      <c r="Q51" s="7">
+        <v>4501</v>
+      </c>
       <c r="R51" s="7">
-        <v>187678</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>29387</v>
+      </c>
+      <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -4661,7 +4995,7 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="AA51" s="7" t="s">
         <v>41</v>
@@ -4675,7 +5009,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026040041</v>
+        <v>2026040537</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4684,44 +5018,48 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
+      <c r="Q52" s="3">
+        <v>4501</v>
+      </c>
       <c r="R52" s="3">
-        <v>187678</v>
-      </c>
-      <c r="S52" s="3"/>
+        <v>29387</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
@@ -4729,11 +5067,9 @@
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
     </row>
     <row r="53" spans="1:28">
@@ -4741,7 +5077,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026040151</v>
+        <v>2026040486</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4750,46 +5086,44 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7">
-        <v>120858</v>
-      </c>
-      <c r="S53" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>177932</v>
+      </c>
+      <c r="S53" s="7"/>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
       <c r="V53" s="7"/>
@@ -4797,7 +5131,7 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="AA53" s="7"/>
       <c r="AB53" s="7"/>
@@ -4807,7 +5141,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026040152</v>
+        <v>2026040485</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -4816,44 +5150,46 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>120858</v>
-      </c>
-      <c r="S54" s="3"/>
+        <v>177932</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
@@ -4861,11 +5197,9 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
     </row>
     <row r="55" spans="1:28">
@@ -4873,7 +5207,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026040439</v>
+        <v>2026040161</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -4882,44 +5216,38 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>146</v>
+        <v>211</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K55" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
       <c r="L55" s="8" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>45</v>
       </c>
       <c r="P55" s="7"/>
-      <c r="Q55" s="7">
-        <v>27727</v>
-      </c>
+      <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>47856</v>
+        <v>0</v>
       </c>
       <c r="S55" s="7" t="s">
         <v>41</v>
@@ -4931,17 +5259,21 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA55" s="7"/>
-      <c r="AB55" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB55" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:28">
       <c r="A56" s="3">
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026040440</v>
+        <v>2026040157</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -4950,46 +5282,42 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
       <c r="L56" s="6" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P56" s="3"/>
-      <c r="Q56" s="3">
-        <v>27727</v>
-      </c>
+      <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>47856</v>
-      </c>
-      <c r="S56" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
@@ -4997,19 +5325,21 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="AA56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB56" s="3"/>
+      <c r="AB56" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:28">
       <c r="A57" s="7">
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026040481</v>
+        <v>2026040825</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5018,34 +5348,30 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
       <c r="L57" s="8" t="s">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="O57" s="7" t="s">
         <v>45</v>
@@ -5053,7 +5379,7 @@
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="7">
-        <v>26583</v>
+        <v>0</v>
       </c>
       <c r="S57" s="7" t="s">
         <v>41</v>
@@ -5065,17 +5391,21 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA57" s="7"/>
-      <c r="AB57" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA57" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB57" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:28">
       <c r="A58" s="3">
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026040482</v>
+        <v>2026041060</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5084,44 +5414,42 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
       <c r="L58" s="6" t="s">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3">
-        <v>26583</v>
-      </c>
-      <c r="S58" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
@@ -5129,19 +5457,21 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB58" s="3"/>
+      <c r="AB58" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:28">
       <c r="A59" s="7">
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026040141</v>
+        <v>2026041063</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5150,34 +5480,30 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
       <c r="L59" s="8" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="N59" s="8" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="O59" s="7" t="s">
         <v>45</v>
@@ -5185,7 +5511,7 @@
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
       <c r="R59" s="7">
-        <v>16836</v>
+        <v>0</v>
       </c>
       <c r="S59" s="7" t="s">
         <v>41</v>
@@ -5197,17 +5523,21 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA59" s="7"/>
-      <c r="AB59" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA59" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB59" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:28">
       <c r="A60" s="3">
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026040142</v>
+        <v>2026040111</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5216,44 +5546,42 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
       <c r="L60" s="6" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3">
-        <v>16836</v>
-      </c>
-      <c r="S60" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -5261,19 +5589,21 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="6" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB60" s="3"/>
+      <c r="AB60" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:28">
       <c r="A61" s="7">
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026040143</v>
+        <v>2026040563</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5282,46 +5612,44 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="L61" s="8" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7">
-        <v>69969</v>
-      </c>
-      <c r="S61" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S61" s="7"/>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
@@ -5329,17 +5657,21 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA61" s="7"/>
-      <c r="AB61" s="7"/>
+        <v>235</v>
+      </c>
+      <c r="AA61" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB61" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:28">
       <c r="A62" s="3">
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026040144</v>
+        <v>2026040561</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5348,42 +5680,42 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>62</v>
+        <v>236</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3">
-        <v>69969</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
@@ -5393,19 +5725,21 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB62" s="3"/>
+      <c r="AB62" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:28">
       <c r="A63" s="7">
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026040149</v>
+        <v>2026041056</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5414,34 +5748,30 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K63" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
       <c r="L63" s="8" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="O63" s="7" t="s">
         <v>45</v>
@@ -5449,7 +5779,7 @@
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
       <c r="R63" s="7">
-        <v>155088</v>
+        <v>0</v>
       </c>
       <c r="S63" s="7" t="s">
         <v>41</v>
@@ -5461,17 +5791,21 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA63" s="7"/>
-      <c r="AB63" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="AA63" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB63" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:28">
       <c r="A64" s="3">
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026040150</v>
+        <v>2026040123</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5480,44 +5814,42 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
       <c r="L64" s="6" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3">
-        <v>155088</v>
-      </c>
-      <c r="S64" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -5525,19 +5857,21 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="AA64" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB64" s="3"/>
+      <c r="AB64" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:28">
       <c r="A65" s="7">
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026040147</v>
+        <v>2026040806</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5546,34 +5880,30 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>62</v>
+        <v>247</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K65" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
       <c r="L65" s="8" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="N65" s="8" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="O65" s="7" t="s">
         <v>45</v>
@@ -5581,7 +5911,7 @@
       <c r="P65" s="7"/>
       <c r="Q65" s="7"/>
       <c r="R65" s="7">
-        <v>116077</v>
+        <v>0</v>
       </c>
       <c r="S65" s="7" t="s">
         <v>41</v>
@@ -5593,17 +5923,21 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA65" s="7"/>
-      <c r="AB65" s="7"/>
+        <v>252</v>
+      </c>
+      <c r="AA65" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB65" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:28">
       <c r="A66" s="3">
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026040148</v>
+        <v>2026040557</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -5612,44 +5946,50 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="P66" s="3">
+        <v>2166</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>3083</v>
+      </c>
       <c r="R66" s="3">
-        <v>116077</v>
-      </c>
-      <c r="S66" s="3"/>
+        <v>11005</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -5657,19 +5997,21 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB66" s="3"/>
+      <c r="AB66" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:28">
       <c r="A67" s="7">
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026040099</v>
+        <v>2026040558</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -5678,42 +6020,46 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>89</v>
+        <v>254</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="N67" s="8" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="O67" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="P67" s="7"/>
-      <c r="Q67" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="P67" s="7">
+        <v>2166</v>
+      </c>
+      <c r="Q67" s="7">
+        <v>3083</v>
+      </c>
       <c r="R67" s="7">
-        <v>0</v>
+        <v>11005</v>
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
@@ -5723,21 +6069,19 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
       <c r="Z67" s="8" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="AA67" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB67" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB67" s="7"/>
     </row>
     <row r="68" spans="1:28">
       <c r="A68" s="3">
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026040195</v>
+        <v>2026040916</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -5746,38 +6090,44 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
+        <v>259</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L68" s="6" t="s">
-        <v>102</v>
+        <v>260</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
+      <c r="Q68" s="3">
+        <v>1500</v>
+      </c>
       <c r="R68" s="3">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="S68" s="3" t="s">
         <v>41</v>
@@ -5791,7 +6141,7 @@
         <v>41</v>
       </c>
       <c r="Z68" s="6" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="AA68" s="3" t="s">
         <v>41</v>
@@ -5805,7 +6155,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026040050</v>
+        <v>2026040917</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -5814,68 +6164,66 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
+        <v>259</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L69" s="8" t="s">
-        <v>102</v>
+        <v>260</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="N69" s="8" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
+      <c r="Q69" s="7">
+        <v>1500</v>
+      </c>
       <c r="R69" s="7">
-        <v>0</v>
-      </c>
-      <c r="S69" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>22500</v>
+      </c>
+      <c r="S69" s="7"/>
       <c r="T69" s="7"/>
-      <c r="U69" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U69" s="7"/>
       <c r="V69" s="7"/>
       <c r="W69" s="7"/>
       <c r="X69" s="7"/>
-      <c r="Y69" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y69" s="7"/>
       <c r="Z69" s="8" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="AA69" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB69" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB69" s="7"/>
     </row>
     <row r="70" spans="1:28">
       <c r="A70" s="3">
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026040200</v>
+        <v>2026040559</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -5884,44 +6232,50 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>174</v>
+        <v>263</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="P70" s="3">
+        <v>451</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>1368</v>
+      </c>
       <c r="R70" s="3">
-        <v>0</v>
-      </c>
-      <c r="S70" s="3"/>
+        <v>8005</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
@@ -5929,7 +6283,7 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="6" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="AA70" s="3" t="s">
         <v>41</v>
@@ -5943,7 +6297,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026040511</v>
+        <v>2026040560</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -5952,66 +6306,68 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
+        <v>264</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L71" s="8" t="s">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="O71" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="P71" s="7">
+        <v>451</v>
+      </c>
+      <c r="Q71" s="7">
+        <v>1368</v>
+      </c>
       <c r="R71" s="7">
-        <v>0</v>
-      </c>
-      <c r="S71" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>8005</v>
+      </c>
+      <c r="S71" s="7"/>
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
       <c r="W71" s="7"/>
       <c r="X71" s="7"/>
-      <c r="Y71" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y71" s="7"/>
       <c r="Z71" s="8" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="AA71" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB71" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB71" s="7"/>
     </row>
     <row r="72" spans="1:28">
       <c r="A72" s="3">
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026040469</v>
+        <v>2026040034</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6020,52 +6376,54 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>146</v>
+        <v>267</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>239</v>
+        <v>70</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
+        <v>268</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L72" s="6" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
+      <c r="Q72" s="3">
+        <v>377</v>
+      </c>
       <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>3241</v>
+      </c>
+      <c r="S72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
-      <c r="Y72" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y72" s="3"/>
       <c r="Z72" s="6" t="s">
-        <v>112</v>
+        <v>258</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>41</v>
@@ -6079,7 +6437,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026040209</v>
+        <v>2026040033</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6088,44 +6446,48 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="O73" s="7" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="P73" s="7"/>
-      <c r="Q73" s="7"/>
+      <c r="Q73" s="7">
+        <v>377</v>
+      </c>
       <c r="R73" s="7">
-        <v>0</v>
-      </c>
-      <c r="S73" s="7"/>
+        <v>3241</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
@@ -6133,7 +6495,7 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="8" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="AA73" s="7" t="s">
         <v>41</v>
@@ -6145,7 +6507,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026040430</v>
+        <v>2026040434</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6154,52 +6516,58 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>246</v>
+        <v>70</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>248</v>
+        <v>35</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
+      <c r="Q74" s="3">
+        <v>377</v>
+      </c>
       <c r="R74" s="3">
-        <v>0</v>
+        <v>3241</v>
       </c>
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
+      <c r="W74" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
+      <c r="Y74" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z74" s="6" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="AA74" s="3" t="s">
         <v>41</v>
@@ -6209,37 +6577,2925 @@
       </c>
     </row>
     <row r="75" spans="1:28">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
-      <c r="K75" s="9"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
-      <c r="N75" s="10"/>
-      <c r="O75" s="9"/>
-      <c r="P75" s="9"/>
-      <c r="Q75" s="9"/>
-      <c r="R75" s="9"/>
-      <c r="S75" s="9"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="10"/>
-      <c r="AA75" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="AB75" s="9">
-        <v>34</v>
+      <c r="A75" s="7">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7">
+        <v>2026040914</v>
+      </c>
+      <c r="C75" s="7">
+        <v>1</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="M75" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="N75" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="O75" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="7">
+        <v>53451</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T75" s="7"/>
+      <c r="U75" s="7"/>
+      <c r="V75" s="7"/>
+      <c r="W75" s="7"/>
+      <c r="X75" s="7"/>
+      <c r="Y75" s="7"/>
+      <c r="Z75" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA75" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB75" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28">
+      <c r="A76" s="3">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3">
+        <v>2026040915</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3">
+        <v>53451</v>
+      </c>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB76" s="3"/>
+    </row>
+    <row r="77" spans="1:28">
+      <c r="A77" s="7">
+        <v>75</v>
+      </c>
+      <c r="B77" s="7">
+        <v>2026040832</v>
+      </c>
+      <c r="C77" s="7">
+        <v>1</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="N77" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="O77" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="7">
+        <v>86361</v>
+      </c>
+      <c r="S77" s="7"/>
+      <c r="T77" s="7"/>
+      <c r="U77" s="7"/>
+      <c r="V77" s="7"/>
+      <c r="W77" s="7"/>
+      <c r="X77" s="7"/>
+      <c r="Y77" s="7"/>
+      <c r="Z77" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA77" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB77" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28">
+      <c r="A78" s="3">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3">
+        <v>2026040831</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3">
+        <v>86361</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA78" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB78" s="3"/>
+    </row>
+    <row r="79" spans="1:28">
+      <c r="A79" s="7">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7">
+        <v>2026040038</v>
+      </c>
+      <c r="C79" s="7">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="7">
+        <v>185800</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T79" s="7"/>
+      <c r="U79" s="7"/>
+      <c r="V79" s="7"/>
+      <c r="W79" s="7"/>
+      <c r="X79" s="7"/>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA79" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB79" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28">
+      <c r="A80" s="3">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3">
+        <v>2026040039</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3">
+        <v>185800</v>
+      </c>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB80" s="3"/>
+    </row>
+    <row r="81" spans="1:28">
+      <c r="A81" s="7">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7">
+        <v>2026040040</v>
+      </c>
+      <c r="C81" s="7">
+        <v>1</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="N81" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7">
+        <v>187678</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7"/>
+      <c r="V81" s="7"/>
+      <c r="W81" s="7"/>
+      <c r="X81" s="7"/>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA81" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB81" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28">
+      <c r="A82" s="3">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2026040041</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3">
+        <v>187678</v>
+      </c>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA82" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="1:28">
+      <c r="A83" s="7">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7">
+        <v>2026041044</v>
+      </c>
+      <c r="C83" s="7">
+        <v>1</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N83" s="8"/>
+      <c r="O83" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7">
+        <v>62000</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T83" s="7"/>
+      <c r="U83" s="7"/>
+      <c r="V83" s="7"/>
+      <c r="W83" s="7"/>
+      <c r="X83" s="7"/>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA83" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB83" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28">
+      <c r="A84" s="3">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2026041045</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="N84" s="6"/>
+      <c r="O84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3">
+        <v>62000</v>
+      </c>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA84" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB84" s="3"/>
+    </row>
+    <row r="85" spans="1:28">
+      <c r="A85" s="7">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7">
+        <v>2026040830</v>
+      </c>
+      <c r="C85" s="7">
+        <v>1</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="N85" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="O85" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
+      <c r="R85" s="7">
+        <v>6841</v>
+      </c>
+      <c r="S85" s="7"/>
+      <c r="T85" s="7"/>
+      <c r="U85" s="7"/>
+      <c r="V85" s="7"/>
+      <c r="W85" s="7"/>
+      <c r="X85" s="7"/>
+      <c r="Y85" s="7"/>
+      <c r="Z85" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA85" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB85" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28">
+      <c r="A86" s="3">
+        <v>84</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2026040829</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3">
+        <v>6841</v>
+      </c>
+      <c r="S86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB86" s="3"/>
+    </row>
+    <row r="87" spans="1:28">
+      <c r="A87" s="7">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7">
+        <v>2026040151</v>
+      </c>
+      <c r="C87" s="7">
+        <v>1</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="M87" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="N87" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="O87" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
+      <c r="R87" s="7">
+        <v>120858</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T87" s="7"/>
+      <c r="U87" s="7"/>
+      <c r="V87" s="7"/>
+      <c r="W87" s="7"/>
+      <c r="X87" s="7"/>
+      <c r="Y87" s="7"/>
+      <c r="Z87" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA87" s="7"/>
+      <c r="AB87" s="7"/>
+    </row>
+    <row r="88" spans="1:28">
+      <c r="A88" s="3">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2026040152</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3">
+        <v>120858</v>
+      </c>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA88" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB88" s="3"/>
+    </row>
+    <row r="89" spans="1:28">
+      <c r="A89" s="7">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7">
+        <v>2026040439</v>
+      </c>
+      <c r="C89" s="7">
+        <v>1</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K89" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="M89" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="N89" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="O89" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7">
+        <v>27727</v>
+      </c>
+      <c r="R89" s="7">
+        <v>47856</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T89" s="7"/>
+      <c r="U89" s="7"/>
+      <c r="V89" s="7"/>
+      <c r="W89" s="7"/>
+      <c r="X89" s="7"/>
+      <c r="Y89" s="7"/>
+      <c r="Z89" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA89" s="7"/>
+      <c r="AB89" s="7"/>
+    </row>
+    <row r="90" spans="1:28">
+      <c r="A90" s="3">
+        <v>88</v>
+      </c>
+      <c r="B90" s="3">
+        <v>2026040440</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3">
+        <v>27727</v>
+      </c>
+      <c r="R90" s="3">
+        <v>47856</v>
+      </c>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA90" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="1:28">
+      <c r="A91" s="7">
+        <v>89</v>
+      </c>
+      <c r="B91" s="7">
+        <v>2026040481</v>
+      </c>
+      <c r="C91" s="7">
+        <v>1</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K91" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="M91" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N91" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="O91" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
+      <c r="R91" s="7">
+        <v>26583</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T91" s="7"/>
+      <c r="U91" s="7"/>
+      <c r="V91" s="7"/>
+      <c r="W91" s="7"/>
+      <c r="X91" s="7"/>
+      <c r="Y91" s="7"/>
+      <c r="Z91" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA91" s="7"/>
+      <c r="AB91" s="7"/>
+    </row>
+    <row r="92" spans="1:28">
+      <c r="A92" s="3">
+        <v>90</v>
+      </c>
+      <c r="B92" s="3">
+        <v>2026040482</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3">
+        <v>26583</v>
+      </c>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA92" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB92" s="3"/>
+    </row>
+    <row r="93" spans="1:28">
+      <c r="A93" s="7">
+        <v>91</v>
+      </c>
+      <c r="B93" s="7">
+        <v>2026040141</v>
+      </c>
+      <c r="C93" s="7">
+        <v>1</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="M93" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="N93" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="O93" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
+      <c r="R93" s="7">
+        <v>16836</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T93" s="7"/>
+      <c r="U93" s="7"/>
+      <c r="V93" s="7"/>
+      <c r="W93" s="7"/>
+      <c r="X93" s="7"/>
+      <c r="Y93" s="7"/>
+      <c r="Z93" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA93" s="7"/>
+      <c r="AB93" s="7"/>
+    </row>
+    <row r="94" spans="1:28">
+      <c r="A94" s="3">
+        <v>92</v>
+      </c>
+      <c r="B94" s="3">
+        <v>2026040142</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3">
+        <v>16836</v>
+      </c>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB94" s="3"/>
+    </row>
+    <row r="95" spans="1:28">
+      <c r="A95" s="7">
+        <v>93</v>
+      </c>
+      <c r="B95" s="7">
+        <v>2026040143</v>
+      </c>
+      <c r="C95" s="7">
+        <v>1</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="N95" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="O95" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+      <c r="R95" s="7">
+        <v>69969</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T95" s="7"/>
+      <c r="U95" s="7"/>
+      <c r="V95" s="7"/>
+      <c r="W95" s="7"/>
+      <c r="X95" s="7"/>
+      <c r="Y95" s="7"/>
+      <c r="Z95" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA95" s="7"/>
+      <c r="AB95" s="7"/>
+    </row>
+    <row r="96" spans="1:28">
+      <c r="A96" s="3">
+        <v>94</v>
+      </c>
+      <c r="B96" s="3">
+        <v>2026040144</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3">
+        <v>69969</v>
+      </c>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="3"/>
+      <c r="Y96" s="3"/>
+      <c r="Z96" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA96" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB96" s="3"/>
+    </row>
+    <row r="97" spans="1:28">
+      <c r="A97" s="7">
+        <v>95</v>
+      </c>
+      <c r="B97" s="7">
+        <v>2026040149</v>
+      </c>
+      <c r="C97" s="7">
+        <v>1</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="M97" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="N97" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="O97" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="7">
+        <v>155088</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T97" s="7"/>
+      <c r="U97" s="7"/>
+      <c r="V97" s="7"/>
+      <c r="W97" s="7"/>
+      <c r="X97" s="7"/>
+      <c r="Y97" s="7"/>
+      <c r="Z97" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA97" s="7"/>
+      <c r="AB97" s="7"/>
+    </row>
+    <row r="98" spans="1:28">
+      <c r="A98" s="3">
+        <v>96</v>
+      </c>
+      <c r="B98" s="3">
+        <v>2026040150</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3">
+        <v>155088</v>
+      </c>
+      <c r="S98" s="3"/>
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3"/>
+      <c r="Z98" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA98" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB98" s="3"/>
+    </row>
+    <row r="99" spans="1:28">
+      <c r="A99" s="7">
+        <v>97</v>
+      </c>
+      <c r="B99" s="7">
+        <v>2026040147</v>
+      </c>
+      <c r="C99" s="7">
+        <v>1</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="M99" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="N99" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="O99" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P99" s="7"/>
+      <c r="Q99" s="7"/>
+      <c r="R99" s="7">
+        <v>116077</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T99" s="7"/>
+      <c r="U99" s="7"/>
+      <c r="V99" s="7"/>
+      <c r="W99" s="7"/>
+      <c r="X99" s="7"/>
+      <c r="Y99" s="7"/>
+      <c r="Z99" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA99" s="7"/>
+      <c r="AB99" s="7"/>
+    </row>
+    <row r="100" spans="1:28">
+      <c r="A100" s="3">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3">
+        <v>2026040148</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3">
+        <v>116077</v>
+      </c>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+      <c r="X100" s="3"/>
+      <c r="Y100" s="3"/>
+      <c r="Z100" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB100" s="3"/>
+    </row>
+    <row r="101" spans="1:28">
+      <c r="A101" s="7">
+        <v>99</v>
+      </c>
+      <c r="B101" s="7">
+        <v>2026040099</v>
+      </c>
+      <c r="C101" s="7">
+        <v>1</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="N101" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="O101" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="P101" s="7"/>
+      <c r="Q101" s="7"/>
+      <c r="R101" s="7">
+        <v>0</v>
+      </c>
+      <c r="S101" s="7"/>
+      <c r="T101" s="7"/>
+      <c r="U101" s="7"/>
+      <c r="V101" s="7"/>
+      <c r="W101" s="7"/>
+      <c r="X101" s="7"/>
+      <c r="Y101" s="7"/>
+      <c r="Z101" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="AA101" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB101" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28">
+      <c r="A102" s="3">
+        <v>100</v>
+      </c>
+      <c r="B102" s="3">
+        <v>2026040195</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T102" s="3"/>
+      <c r="U102" s="3"/>
+      <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
+      <c r="X102" s="3"/>
+      <c r="Y102" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z102" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28">
+      <c r="A103" s="7">
+        <v>101</v>
+      </c>
+      <c r="B103" s="7">
+        <v>2026040050</v>
+      </c>
+      <c r="C103" s="7">
+        <v>1</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M103" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="N103" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="O103" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P103" s="7"/>
+      <c r="Q103" s="7"/>
+      <c r="R103" s="7">
+        <v>0</v>
+      </c>
+      <c r="S103" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T103" s="7"/>
+      <c r="U103" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V103" s="7"/>
+      <c r="W103" s="7"/>
+      <c r="X103" s="7"/>
+      <c r="Y103" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z103" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA103" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB103" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28">
+      <c r="A104" s="3">
+        <v>102</v>
+      </c>
+      <c r="B104" s="3">
+        <v>2026040200</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3">
+        <v>0</v>
+      </c>
+      <c r="S104" s="3"/>
+      <c r="T104" s="3"/>
+      <c r="U104" s="3"/>
+      <c r="V104" s="3"/>
+      <c r="W104" s="3"/>
+      <c r="X104" s="3"/>
+      <c r="Y104" s="3"/>
+      <c r="Z104" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AA104" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB104" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28">
+      <c r="A105" s="7">
+        <v>103</v>
+      </c>
+      <c r="B105" s="7">
+        <v>2026040511</v>
+      </c>
+      <c r="C105" s="7">
+        <v>1</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M105" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="N105" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="O105" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P105" s="7"/>
+      <c r="Q105" s="7"/>
+      <c r="R105" s="7">
+        <v>0</v>
+      </c>
+      <c r="S105" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T105" s="7"/>
+      <c r="U105" s="7"/>
+      <c r="V105" s="7"/>
+      <c r="W105" s="7"/>
+      <c r="X105" s="7"/>
+      <c r="Y105" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z105" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA105" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB105" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28">
+      <c r="A106" s="3">
+        <v>104</v>
+      </c>
+      <c r="B106" s="3">
+        <v>2026040598</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L106" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3">
+        <v>0</v>
+      </c>
+      <c r="S106" s="3"/>
+      <c r="T106" s="3"/>
+      <c r="U106" s="3"/>
+      <c r="V106" s="3"/>
+      <c r="W106" s="3"/>
+      <c r="X106" s="3"/>
+      <c r="Y106" s="3"/>
+      <c r="Z106" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA106" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28">
+      <c r="A107" s="7">
+        <v>105</v>
+      </c>
+      <c r="B107" s="7">
+        <v>2026040599</v>
+      </c>
+      <c r="C107" s="7">
+        <v>1</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M107" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="N107" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="O107" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="P107" s="7"/>
+      <c r="Q107" s="7"/>
+      <c r="R107" s="7">
+        <v>0</v>
+      </c>
+      <c r="S107" s="7"/>
+      <c r="T107" s="7"/>
+      <c r="U107" s="7"/>
+      <c r="V107" s="7"/>
+      <c r="W107" s="7"/>
+      <c r="X107" s="7"/>
+      <c r="Y107" s="7"/>
+      <c r="Z107" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA107" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB107" s="7"/>
+    </row>
+    <row r="108" spans="1:28">
+      <c r="A108" s="3">
+        <v>106</v>
+      </c>
+      <c r="B108" s="3">
+        <v>2026040661</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3">
+        <v>0</v>
+      </c>
+      <c r="S108" s="3"/>
+      <c r="T108" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="U108" s="3"/>
+      <c r="V108" s="3"/>
+      <c r="W108" s="3"/>
+      <c r="X108" s="3"/>
+      <c r="Y108" s="3"/>
+      <c r="Z108" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="AA108" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB108" s="3"/>
+    </row>
+    <row r="109" spans="1:28">
+      <c r="A109" s="7">
+        <v>107</v>
+      </c>
+      <c r="B109" s="7">
+        <v>2026040585</v>
+      </c>
+      <c r="C109" s="7">
+        <v>1</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M109" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="N109" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="P109" s="7"/>
+      <c r="Q109" s="7"/>
+      <c r="R109" s="7">
+        <v>0</v>
+      </c>
+      <c r="S109" s="7"/>
+      <c r="T109" s="7"/>
+      <c r="U109" s="7"/>
+      <c r="V109" s="7"/>
+      <c r="W109" s="7"/>
+      <c r="X109" s="7"/>
+      <c r="Y109" s="7"/>
+      <c r="Z109" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="AA109" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB109" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28">
+      <c r="A110" s="3">
+        <v>108</v>
+      </c>
+      <c r="B110" s="3">
+        <v>2026040907</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L110" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="3"/>
+      <c r="R110" s="3">
+        <v>0</v>
+      </c>
+      <c r="S110" s="3"/>
+      <c r="T110" s="3"/>
+      <c r="U110" s="3"/>
+      <c r="V110" s="3"/>
+      <c r="W110" s="3"/>
+      <c r="X110" s="3"/>
+      <c r="Y110" s="3"/>
+      <c r="Z110" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA110" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB110" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28">
+      <c r="A111" s="7">
+        <v>109</v>
+      </c>
+      <c r="B111" s="7">
+        <v>2026041049</v>
+      </c>
+      <c r="C111" s="7">
+        <v>1</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M111" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="N111" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="O111" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P111" s="7"/>
+      <c r="Q111" s="7"/>
+      <c r="R111" s="7">
+        <v>0</v>
+      </c>
+      <c r="S111" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T111" s="7"/>
+      <c r="U111" s="7"/>
+      <c r="V111" s="7"/>
+      <c r="W111" s="7"/>
+      <c r="X111" s="7"/>
+      <c r="Y111" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z111" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA111" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB111" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28">
+      <c r="A112" s="3">
+        <v>110</v>
+      </c>
+      <c r="B112" s="3">
+        <v>2026040469</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="N112" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P112" s="3"/>
+      <c r="Q112" s="3"/>
+      <c r="R112" s="3">
+        <v>0</v>
+      </c>
+      <c r="S112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T112" s="3"/>
+      <c r="U112" s="3"/>
+      <c r="V112" s="3"/>
+      <c r="W112" s="3"/>
+      <c r="X112" s="3"/>
+      <c r="Y112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z112" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28">
+      <c r="A113" s="7">
+        <v>111</v>
+      </c>
+      <c r="B113" s="7">
+        <v>2026040209</v>
+      </c>
+      <c r="C113" s="7">
+        <v>1</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M113" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="N113" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="O113" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="P113" s="7"/>
+      <c r="Q113" s="7"/>
+      <c r="R113" s="7">
+        <v>0</v>
+      </c>
+      <c r="S113" s="7"/>
+      <c r="T113" s="7"/>
+      <c r="U113" s="7"/>
+      <c r="V113" s="7"/>
+      <c r="W113" s="7"/>
+      <c r="X113" s="7"/>
+      <c r="Y113" s="7"/>
+      <c r="Z113" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="AA113" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB113" s="7"/>
+    </row>
+    <row r="114" spans="1:28">
+      <c r="A114" s="3">
+        <v>112</v>
+      </c>
+      <c r="B114" s="3">
+        <v>2026040788</v>
+      </c>
+      <c r="C114" s="3">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="L114" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P114" s="3"/>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="3">
+        <v>0</v>
+      </c>
+      <c r="S114" s="3"/>
+      <c r="T114" s="3"/>
+      <c r="U114" s="3"/>
+      <c r="V114" s="3"/>
+      <c r="W114" s="3"/>
+      <c r="X114" s="3"/>
+      <c r="Y114" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z114" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="AA114" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB114" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28">
+      <c r="A115" s="7">
+        <v>113</v>
+      </c>
+      <c r="B115" s="7">
+        <v>2026040430</v>
+      </c>
+      <c r="C115" s="7">
+        <v>1</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M115" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="N115" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="O115" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="P115" s="7"/>
+      <c r="Q115" s="7"/>
+      <c r="R115" s="7">
+        <v>0</v>
+      </c>
+      <c r="S115" s="7"/>
+      <c r="T115" s="7"/>
+      <c r="U115" s="7"/>
+      <c r="V115" s="7"/>
+      <c r="W115" s="7"/>
+      <c r="X115" s="7"/>
+      <c r="Y115" s="7"/>
+      <c r="Z115" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA115" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB115" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28">
+      <c r="A116" s="3">
+        <v>114</v>
+      </c>
+      <c r="B116" s="3">
+        <v>2026040568</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L116" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P116" s="3"/>
+      <c r="Q116" s="3"/>
+      <c r="R116" s="3">
+        <v>0</v>
+      </c>
+      <c r="S116" s="3"/>
+      <c r="T116" s="3"/>
+      <c r="U116" s="3"/>
+      <c r="V116" s="3"/>
+      <c r="W116" s="3"/>
+      <c r="X116" s="3"/>
+      <c r="Y116" s="3"/>
+      <c r="Z116" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="AA116" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB116" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28">
+      <c r="A117" s="7">
+        <v>115</v>
+      </c>
+      <c r="B117" s="7">
+        <v>2026041055</v>
+      </c>
+      <c r="C117" s="7">
+        <v>1</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="J117" s="7"/>
+      <c r="K117" s="7"/>
+      <c r="L117" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M117" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="N117" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="O117" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P117" s="7"/>
+      <c r="Q117" s="7"/>
+      <c r="R117" s="7">
+        <v>0</v>
+      </c>
+      <c r="S117" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T117" s="7"/>
+      <c r="U117" s="7"/>
+      <c r="V117" s="7"/>
+      <c r="W117" s="7"/>
+      <c r="X117" s="7"/>
+      <c r="Y117" s="7"/>
+      <c r="Z117" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA117" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB117" s="7"/>
+    </row>
+    <row r="118" spans="1:28">
+      <c r="A118" s="9"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="9"/>
+      <c r="I118" s="9"/>
+      <c r="J118" s="9"/>
+      <c r="K118" s="9"/>
+      <c r="L118" s="10"/>
+      <c r="M118" s="10"/>
+      <c r="N118" s="10"/>
+      <c r="O118" s="9"/>
+      <c r="P118" s="9"/>
+      <c r="Q118" s="9"/>
+      <c r="R118" s="9"/>
+      <c r="S118" s="9"/>
+      <c r="T118" s="9"/>
+      <c r="U118" s="9"/>
+      <c r="V118" s="9"/>
+      <c r="W118" s="9"/>
+      <c r="X118" s="9"/>
+      <c r="Y118" s="9"/>
+      <c r="Z118" s="10"/>
+      <c r="AA118" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB118" s="9">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202604_Service_Count_Report.xlsx
+++ b/IM/202604_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$118</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$127</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="388">
   <si>
     <t>服務次數統計表        篩選月份：202604</t>
   </si>
@@ -293,6 +293,15 @@
     <t>全部紙夾調成厚紙模式</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>換溫控 上熱 下熱 改回一般</t>
+  </si>
+  <si>
     <t>14:29:00</t>
   </si>
   <si>
@@ -425,9 +434,6 @@
     <t>裝潢回裝完工 已回報0800</t>
   </si>
   <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
     <t>PMQ1 7210002775</t>
   </si>
   <si>
@@ -465,6 +471,18 @@
   </si>
   <si>
     <t>軌道卡異物</t>
+  </si>
+  <si>
+    <t>16:38:00</t>
+  </si>
+  <si>
+    <t>THILF0C216</t>
+  </si>
+  <si>
+    <t>新北市中和區興南路二段118號</t>
+  </si>
+  <si>
+    <t>中和南勢店</t>
   </si>
   <si>
     <t>12:00:00</t>
@@ -730,6 +748,42 @@
     <t>淡水莊園店</t>
   </si>
   <si>
+    <t>15:20:00</t>
+  </si>
+  <si>
+    <t>THILF04298</t>
+  </si>
+  <si>
+    <t>新北市淡水區後洲路一段50號、50之1號1樓</t>
+  </si>
+  <si>
+    <t>淡水後洲店</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>THILF04529</t>
+  </si>
+  <si>
+    <t>新北市淡水區新市二路二段52、56、58、60號一樓全部</t>
+  </si>
+  <si>
+    <t>淡水新洲店</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>THILF04541</t>
+  </si>
+  <si>
+    <t>新北市淡水區濱海路三段140、142號</t>
+  </si>
+  <si>
+    <t>淡水海天店</t>
+  </si>
+  <si>
     <t>12:40:00</t>
   </si>
   <si>
@@ -753,6 +807,15 @@
 換上8119011505</t>
   </si>
   <si>
+    <t>THILF04788</t>
+  </si>
+  <si>
+    <t>新北市淡水區新市五路二段51、53、55號</t>
+  </si>
+  <si>
+    <t>淡水國家店</t>
+  </si>
+  <si>
     <t>11:50:00</t>
   </si>
   <si>
@@ -801,9 +864,6 @@
     <t>湯家瑋</t>
   </si>
   <si>
-    <t>16:30:00</t>
-  </si>
-  <si>
     <t>T252000086</t>
   </si>
   <si>
@@ -958,9 +1018,6 @@
   </si>
   <si>
     <t>五股檢品</t>
-  </si>
-  <si>
-    <t>14:30:00</t>
   </si>
   <si>
     <t>T352800031</t>
@@ -1016,9 +1073,6 @@
     <t>蘆洲中山一</t>
   </si>
   <si>
-    <t>15:20:00</t>
-  </si>
-  <si>
     <t>THILF04025</t>
   </si>
   <si>
@@ -1032,6 +1086,20 @@
   </si>
   <si>
     <t>撤店</t>
+  </si>
+  <si>
+    <t>THILF04218</t>
+  </si>
+  <si>
+    <t>新北市蘆洲區得勝街108號一樓</t>
+  </si>
+  <si>
+    <t>蘆洲湧蓮店</t>
+  </si>
+  <si>
+    <t>更換發票機
+換上8155006320
+換下8155002981</t>
   </si>
   <si>
     <t>2026-04-05</t>
@@ -1102,6 +1170,9 @@
     <t>立式掃描器喇叭異常帶回檢修</t>
   </si>
   <si>
+    <t>設備歸還測試正常</t>
+  </si>
+  <si>
     <t>狄澤洋</t>
   </si>
   <si>
@@ -1118,6 +1189,9 @@
   </si>
   <si>
     <t>更換第一顆硬碟無備份還原</t>
+  </si>
+  <si>
+    <t>12:28:00</t>
   </si>
   <si>
     <t>THILF0D111</t>
@@ -1132,9 +1206,6 @@
     <t>更換T70
 換上 8138001526
 換下 8138001580</t>
-  </si>
-  <si>
-    <t>12:28:00</t>
   </si>
   <si>
     <t>合計</t>
@@ -1551,7 +1622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB118"/>
+  <dimension ref="A1:AB127"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -2509,7 +2580,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026040179</v>
+        <v>2026041147</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2521,7 +2592,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>87</v>
@@ -2530,7 +2601,7 @@
         <v>88</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>77</v>
@@ -2539,23 +2610,23 @@
         <v>36</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>91</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N15" s="8"/>
       <c r="O15" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>32628</v>
-      </c>
-      <c r="S15" s="7"/>
+        <v>136307</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -2563,7 +2634,7 @@
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="8" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
@@ -2577,7 +2648,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026040424</v>
+        <v>2026040179</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2589,16 +2660,16 @@
         <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>77</v>
@@ -2610,22 +2681,20 @@
         <v>65</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>32630</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>32628</v>
+      </c>
+      <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -2647,7 +2716,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026040899</v>
+        <v>2026040424</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2659,39 +2728,43 @@
         <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="N17" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="O17" s="7" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7">
-        <v>70987</v>
-      </c>
-      <c r="S17" s="7"/>
+        <v>32630</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -2699,7 +2772,7 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
@@ -2713,7 +2786,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026040555</v>
+        <v>2026040899</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2725,41 +2798,39 @@
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>127085</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>70987</v>
+      </c>
+      <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -2767,7 +2838,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="6" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>41</v>
@@ -2781,7 +2852,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026040556</v>
+        <v>2026040555</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2796,36 +2867,38 @@
         <v>42</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7">
         <v>127085</v>
       </c>
-      <c r="S19" s="7"/>
+      <c r="S19" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -2838,14 +2911,16 @@
       <c r="AA19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB19" s="7"/>
+      <c r="AB19" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026040539</v>
+        <v>2026040556</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2860,38 +2935,36 @@
         <v>42</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3">
-        <v>228034</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>127085</v>
+      </c>
+      <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
@@ -2904,16 +2977,14 @@
       <c r="AA20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB20" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB20" s="3"/>
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026040540</v>
+        <v>2026040539</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2928,36 +2999,38 @@
         <v>42</v>
       </c>
       <c r="G21" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7">
         <v>228034</v>
       </c>
-      <c r="S21" s="7"/>
+      <c r="S21" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -2970,14 +3043,16 @@
       <c r="AA21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB21" s="7"/>
+      <c r="AB21" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="3">
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026040053</v>
+        <v>2026040540</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2989,43 +3064,39 @@
         <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P22" s="3"/>
-      <c r="Q22" s="3">
-        <v>28637</v>
-      </c>
+      <c r="Q22" s="3"/>
       <c r="R22" s="3">
-        <v>718456</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>228034</v>
+      </c>
+      <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -3035,7 +3106,9 @@
       <c r="Z22" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AA22" s="3"/>
+      <c r="AA22" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB22" s="3"/>
     </row>
     <row r="23" spans="1:28">
@@ -3043,7 +3116,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026040054</v>
+        <v>2026040053</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -3061,13 +3134,13 @@
         <v>71</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
@@ -3080,7 +3153,7 @@
       </c>
       <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7">
@@ -3089,7 +3162,9 @@
       <c r="R23" s="7">
         <v>718456</v>
       </c>
-      <c r="S23" s="7"/>
+      <c r="S23" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -3107,7 +3182,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026040578</v>
+        <v>2026040054</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -3119,7 +3194,7 @@
         <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>71</v>
@@ -3134,24 +3209,24 @@
         <v>116</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>120</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N24" s="6"/>
       <c r="O24" s="3" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3">
+        <v>28637</v>
+      </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>718456</v>
       </c>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -3161,21 +3236,17 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026041011</v>
+        <v>2026040578</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -3190,58 +3261,60 @@
         <v>75</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="H25" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>119</v>
-      </c>
       <c r="N25" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7">
         <v>0</v>
       </c>
-      <c r="S25" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="S25" s="7"/>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
-      <c r="Y25" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB25" s="7"/>
+      <c r="AB25" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026040820</v>
+        <v>2026041011</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -3253,27 +3326,27 @@
         <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>45</v>
@@ -3283,31 +3356,31 @@
       <c r="R26" s="3">
         <v>0</v>
       </c>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
+      <c r="Y26" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z26" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB26" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB26" s="3"/>
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="7">
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026040819</v>
+        <v>2026040820</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -3319,27 +3392,27 @@
         <v>30</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O27" s="7" t="s">
         <v>45</v>
@@ -3349,19 +3422,17 @@
       <c r="R27" s="7">
         <v>0</v>
       </c>
-      <c r="S27" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
-      <c r="Y27" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>41</v>
@@ -3375,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026040591</v>
+        <v>2026040819</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3387,49 +3458,49 @@
         <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
       <c r="L28" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3">
         <v>0</v>
       </c>
-      <c r="S28" s="3"/>
+      <c r="S28" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
+      <c r="Y28" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z28" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>41</v>
@@ -3443,7 +3514,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026040881</v>
+        <v>2026040591</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3455,61 +3526,63 @@
         <v>30</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="H29" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="N29" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>136</v>
-      </c>
       <c r="O29" s="7" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7">
         <v>0</v>
       </c>
-      <c r="S29" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="S29" s="7"/>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
-      <c r="Y29" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB29" s="7"/>
+      <c r="AB29" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026040104</v>
+        <v>2026040881</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3521,63 +3594,61 @@
         <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>140</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
       <c r="L30" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3">
         <v>0</v>
       </c>
-      <c r="S30" s="3"/>
+      <c r="S30" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
+      <c r="Y30" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z30" s="6" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="AA30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB30" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="7">
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026040470</v>
+        <v>2026040104</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3589,49 +3660,49 @@
         <v>30</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G31" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="N31" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="H31" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>149</v>
-      </c>
       <c r="O31" s="7" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
         <v>0</v>
       </c>
-      <c r="S31" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
-      <c r="Y31" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>41</v>
@@ -3645,7 +3716,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026040627</v>
+        <v>2026041166</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3657,27 +3728,27 @@
         <v>30</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>45</v>
@@ -3699,7 +3770,7 @@
         <v>41</v>
       </c>
       <c r="Z32" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>41</v>
@@ -3713,7 +3784,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026040565</v>
+        <v>2026040470</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3725,61 +3796,63 @@
         <v>30</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="H33" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="I33" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>117</v>
-      </c>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
       <c r="L33" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7">
         <v>0</v>
       </c>
-      <c r="S33" s="7"/>
+      <c r="S33" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
+      <c r="Y33" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z33" s="8" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="AA33" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB33" s="7"/>
+      <c r="AB33" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:28">
       <c r="A34" s="3">
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026040422</v>
+        <v>2026040627</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3788,46 +3861,38 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>70</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
       <c r="L34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M34" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="N34" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="P34" s="3">
-        <v>7643</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>16666</v>
-      </c>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>23881</v>
+        <v>0</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>41</v>
@@ -3837,9 +3902,11 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
+      <c r="Y34" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z34" s="6" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="AA34" s="3" t="s">
         <v>41</v>
@@ -3853,7 +3920,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026040423</v>
+        <v>2026040565</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3862,46 +3929,42 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>155</v>
+        <v>30</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>156</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L35" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M35" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="M35" s="8" t="s">
+      <c r="N35" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="N35" s="8" t="s">
-        <v>159</v>
-      </c>
       <c r="O35" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P35" s="7">
-        <v>7643</v>
-      </c>
-      <c r="Q35" s="7">
-        <v>16666</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
       <c r="R35" s="7">
-        <v>23881</v>
+        <v>0</v>
       </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
@@ -3923,7 +3986,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026040487</v>
+        <v>2026040422</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3932,16 +3995,16 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>162</v>
@@ -3964,12 +4027,14 @@
       <c r="O36" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="P36" s="3"/>
+      <c r="P36" s="3">
+        <v>7643</v>
+      </c>
       <c r="Q36" s="3">
-        <v>2082</v>
+        <v>16666</v>
       </c>
       <c r="R36" s="3">
-        <v>105140</v>
+        <v>23881</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>41</v>
@@ -3981,17 +4046,21 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA36" s="3"/>
-      <c r="AB36" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:28">
       <c r="A37" s="7">
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026040488</v>
+        <v>2026040423</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -4000,16 +4069,16 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>162</v>
@@ -4032,12 +4101,14 @@
       <c r="O37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P37" s="7"/>
+      <c r="P37" s="7">
+        <v>7643</v>
+      </c>
       <c r="Q37" s="7">
-        <v>2082</v>
+        <v>16666</v>
       </c>
       <c r="R37" s="7">
-        <v>105140</v>
+        <v>23881</v>
       </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
@@ -4047,9 +4118,11 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA37" s="7"/>
+        <v>166</v>
+      </c>
+      <c r="AA37" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:28">
@@ -4057,7 +4130,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026040498</v>
+        <v>2026040487</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -4066,13 +4139,13 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>167</v>
@@ -4092,44 +4165,40 @@
       <c r="M38" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="N38" s="6"/>
+      <c r="N38" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="O38" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3">
-        <v>288</v>
+        <v>2082</v>
       </c>
       <c r="R38" s="3">
-        <v>15686</v>
+        <v>105140</v>
       </c>
       <c r="S38" s="3" t="s">
         <v>41</v>
       </c>
       <c r="T38" s="3"/>
-      <c r="U38" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB38" s="3">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="7">
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026040499</v>
+        <v>2026040488</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -4138,13 +4207,13 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>167</v>
@@ -4164,16 +4233,18 @@
       <c r="M39" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="N39" s="8"/>
+      <c r="N39" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="O39" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P39" s="7"/>
       <c r="Q39" s="7">
-        <v>288</v>
+        <v>2082</v>
       </c>
       <c r="R39" s="7">
-        <v>15686</v>
+        <v>105140</v>
       </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
@@ -4183,11 +4254,9 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA39" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA39" s="7"/>
       <c r="AB39" s="7"/>
     </row>
     <row r="40" spans="1:28">
@@ -4195,7 +4264,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026040465</v>
+        <v>2026040499</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -4204,7 +4273,7 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>42</v>
@@ -4219,7 +4288,7 @@
         <v>174</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>36</v>
@@ -4230,20 +4299,18 @@
       <c r="M40" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="N40" s="6" t="s">
-        <v>177</v>
-      </c>
+      <c r="N40" s="6"/>
       <c r="O40" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
+      <c r="Q40" s="3">
+        <v>288</v>
+      </c>
       <c r="R40" s="3">
-        <v>303520</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>15686</v>
+      </c>
+      <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
@@ -4251,17 +4318,21 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA40" s="3"/>
-      <c r="AB40" s="3"/>
+        <v>177</v>
+      </c>
+      <c r="AA40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:28">
       <c r="A41" s="7">
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026040466</v>
+        <v>2026040498</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -4270,7 +4341,7 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>42</v>
@@ -4285,7 +4356,7 @@
         <v>174</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
@@ -4296,28 +4367,34 @@
       <c r="M41" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="N41" s="8" t="s">
-        <v>177</v>
-      </c>
+      <c r="N41" s="8"/>
       <c r="O41" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
+      <c r="Q41" s="7">
+        <v>288</v>
+      </c>
       <c r="R41" s="7">
-        <v>303520</v>
-      </c>
-      <c r="S41" s="7"/>
+        <v>15686</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
+      <c r="U41" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA41" s="7"/>
+        <v>177</v>
+      </c>
+      <c r="AA41" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB41" s="7"/>
     </row>
     <row r="42" spans="1:28">
@@ -4325,7 +4402,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026040108</v>
+        <v>2026040465</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4334,10 +4411,10 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>178</v>
@@ -4369,7 +4446,7 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3">
-        <v>27527</v>
+        <v>303520</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>41</v>
@@ -4381,21 +4458,17 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="3"/>
     </row>
     <row r="43" spans="1:28">
       <c r="A43" s="7">
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026040109</v>
+        <v>2026040466</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4404,10 +4477,10 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>178</v>
@@ -4439,7 +4512,7 @@
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>27527</v>
+        <v>303520</v>
       </c>
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
@@ -4449,11 +4522,9 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA43" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA43" s="7"/>
       <c r="AB43" s="7"/>
     </row>
     <row r="44" spans="1:28">
@@ -4461,7 +4532,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026040055</v>
+        <v>2026040108</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4470,42 +4541,46 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="N44" s="6"/>
+        <v>188</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="O44" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>34400</v>
-      </c>
-      <c r="S44" s="3"/>
+        <v>27527</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
@@ -4513,7 +4588,7 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="AA44" s="3" t="s">
         <v>41</v>
@@ -4527,7 +4602,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026040463</v>
+        <v>2026040109</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4536,46 +4611,44 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>92786</v>
-      </c>
-      <c r="S45" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>27527</v>
+      </c>
+      <c r="S45" s="7"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
@@ -4583,9 +4656,11 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA45" s="7"/>
+        <v>166</v>
+      </c>
+      <c r="AA45" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB45" s="7"/>
     </row>
     <row r="46" spans="1:28">
@@ -4593,7 +4668,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026040464</v>
+        <v>2026040055</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4602,19 +4677,19 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>77</v>
@@ -4623,21 +4698,19 @@
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>177</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N46" s="6"/>
       <c r="O46" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3">
-        <v>92786</v>
+        <v>34400</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
@@ -4647,17 +4720,21 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA46" s="3"/>
-      <c r="AB46" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:28">
       <c r="A47" s="7">
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026040791</v>
+        <v>2026040464</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4666,19 +4743,19 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>77</v>
@@ -4687,16 +4764,16 @@
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
@@ -4709,25 +4786,19 @@
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
-      <c r="Y47" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA47" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB47" s="7">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA47" s="7"/>
+      <c r="AB47" s="7"/>
     </row>
     <row r="48" spans="1:28">
       <c r="A48" s="3">
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026040056</v>
+        <v>2026040463</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4736,31 +4807,31 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>183</v>
@@ -4769,11 +4840,9 @@
         <v>45</v>
       </c>
       <c r="P48" s="3"/>
-      <c r="Q48" s="3">
-        <v>2879</v>
-      </c>
+      <c r="Q48" s="3"/>
       <c r="R48" s="3">
-        <v>361051</v>
+        <v>92786</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>41</v>
@@ -4785,21 +4854,17 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA48" s="3"/>
+      <c r="AB48" s="3"/>
     </row>
     <row r="49" spans="1:28">
       <c r="A49" s="7">
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026040057</v>
+        <v>2026040791</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4808,44 +4873,42 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="N49" s="8" t="s">
         <v>183</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7">
-        <v>2879</v>
-      </c>
+      <c r="Q49" s="7"/>
       <c r="R49" s="7">
-        <v>361051</v>
+        <v>92786</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
@@ -4853,21 +4916,25 @@
       <c r="V49" s="7"/>
       <c r="W49" s="7"/>
       <c r="X49" s="7"/>
-      <c r="Y49" s="7"/>
+      <c r="Y49" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z49" s="8" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB49" s="7"/>
+      <c r="AB49" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:28">
       <c r="A50" s="3">
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026040103</v>
+        <v>2026040056</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4876,7 +4943,7 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>31</v>
@@ -4888,22 +4955,22 @@
         <v>197</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>45</v>
@@ -4915,17 +4982,17 @@
       <c r="R50" s="3">
         <v>361051</v>
       </c>
-      <c r="S50" s="3"/>
+      <c r="S50" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T50" s="3"/>
-      <c r="U50" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="AA50" s="3" t="s">
         <v>41</v>
@@ -4939,7 +5006,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026040538</v>
+        <v>2026040057</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4948,44 +5015,44 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="H51" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="J51" s="7" t="s">
         <v>199</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>201</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="O51" s="7" t="s">
         <v>40</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7">
-        <v>4501</v>
+        <v>2879</v>
       </c>
       <c r="R51" s="7">
-        <v>29387</v>
+        <v>361051</v>
       </c>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
@@ -4995,21 +5062,19 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AA51" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB51" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB51" s="7"/>
     </row>
     <row r="52" spans="1:28">
       <c r="A52" s="3">
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026040537</v>
+        <v>2026040103</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -5018,66 +5083,70 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3">
-        <v>4501</v>
+        <v>2879</v>
       </c>
       <c r="R52" s="3">
-        <v>29387</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>361051</v>
+      </c>
+      <c r="S52" s="3"/>
       <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
+      <c r="U52" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA52" s="3"/>
-      <c r="AB52" s="3"/>
+        <v>204</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:28">
       <c r="A53" s="7">
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026040486</v>
+        <v>2026040537</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -5086,16 +5155,16 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G53" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H53" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>206</v>
@@ -5107,23 +5176,27 @@
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P53" s="7"/>
-      <c r="Q53" s="7"/>
+      <c r="Q53" s="7">
+        <v>4501</v>
+      </c>
       <c r="R53" s="7">
-        <v>177932</v>
-      </c>
-      <c r="S53" s="7"/>
+        <v>29387</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
       <c r="V53" s="7"/>
@@ -5131,7 +5204,7 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AA53" s="7"/>
       <c r="AB53" s="7"/>
@@ -5141,7 +5214,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026040485</v>
+        <v>2026040538</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -5150,16 +5223,16 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G54" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>206</v>
@@ -5171,25 +5244,25 @@
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
+      <c r="Q54" s="3">
+        <v>4501</v>
+      </c>
       <c r="R54" s="3">
-        <v>177932</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>29387</v>
+      </c>
+      <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
@@ -5197,9 +5270,11 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA54" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB54" s="3"/>
     </row>
     <row r="55" spans="1:28">
@@ -5207,7 +5282,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026040161</v>
+        <v>2026040485</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -5216,30 +5291,34 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
+      <c r="J55" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L55" s="8" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>45</v>
@@ -5247,7 +5326,7 @@
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>0</v>
+        <v>177932</v>
       </c>
       <c r="S55" s="7" t="s">
         <v>41</v>
@@ -5259,21 +5338,17 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA55" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB55" s="7">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA55" s="7"/>
+      <c r="AB55" s="7"/>
     </row>
     <row r="56" spans="1:28">
       <c r="A56" s="3">
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026040157</v>
+        <v>2026040486</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -5282,42 +5357,44 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G56" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="N56" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>218</v>
-      </c>
       <c r="O56" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>0</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>177932</v>
+      </c>
+      <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
@@ -5325,21 +5402,17 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB56" s="3">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
     </row>
     <row r="57" spans="1:28">
       <c r="A57" s="7">
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026040825</v>
+        <v>2026040161</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5348,30 +5421,30 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
       <c r="L57" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="O57" s="7" t="s">
         <v>45</v>
@@ -5391,7 +5464,7 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA57" s="7" t="s">
         <v>41</v>
@@ -5405,7 +5478,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026041060</v>
+        <v>2026040157</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5414,30 +5487,30 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>223</v>
+        <v>129</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>45</v>
@@ -5457,7 +5530,7 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>41</v>
@@ -5471,7 +5544,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026041063</v>
+        <v>2026040825</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5480,30 +5553,30 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N59" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O59" s="7" t="s">
         <v>45</v>
@@ -5523,7 +5596,7 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA59" s="7" t="s">
         <v>41</v>
@@ -5537,7 +5610,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026040111</v>
+        <v>2026041060</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5546,30 +5619,30 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>45</v>
@@ -5589,7 +5662,7 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>41</v>
@@ -5603,7 +5676,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026040563</v>
+        <v>2026041063</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5612,44 +5685,42 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>75</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>111</v>
+        <v>233</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>117</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
       <c r="L61" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7">
         <v>0</v>
       </c>
-      <c r="S61" s="7"/>
+      <c r="S61" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
@@ -5657,7 +5728,7 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="8" t="s">
-        <v>235</v>
+        <v>126</v>
       </c>
       <c r="AA61" s="7" t="s">
         <v>41</v>
@@ -5671,7 +5742,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026040561</v>
+        <v>2026041136</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5680,44 +5751,42 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>75</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
       <c r="L62" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3"/>
+      <c r="S62" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -5725,7 +5794,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>237</v>
+        <v>126</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>41</v>
@@ -5739,7 +5808,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026041056</v>
+        <v>2026041142</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5748,30 +5817,30 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>75</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>238</v>
+        <v>88</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O63" s="7" t="s">
         <v>45</v>
@@ -5791,7 +5860,7 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA63" s="7" t="s">
         <v>41</v>
@@ -5805,7 +5874,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026040123</v>
+        <v>2026041153</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5814,30 +5883,30 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>243</v>
+        <v>55</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>45</v>
@@ -5857,7 +5926,7 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA64" s="3" t="s">
         <v>41</v>
@@ -5871,7 +5940,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026040806</v>
+        <v>2026040111</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5880,30 +5949,30 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N65" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O65" s="7" t="s">
         <v>45</v>
@@ -5923,7 +5992,7 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="8" t="s">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="AA65" s="7" t="s">
         <v>41</v>
@@ -5937,7 +6006,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026040557</v>
+        <v>2026040563</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -5946,50 +6015,44 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>254</v>
+        <v>114</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P66" s="3">
-        <v>2166</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>3083</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
       <c r="R66" s="3">
-        <v>11005</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -5997,7 +6060,7 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>41</v>
@@ -6011,7 +6074,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026040558</v>
+        <v>2026040561</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -6020,46 +6083,42 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>254</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N67" s="8" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="O67" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P67" s="7">
-        <v>2166</v>
-      </c>
-      <c r="Q67" s="7">
-        <v>3083</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
       <c r="R67" s="7">
-        <v>11005</v>
+        <v>0</v>
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
@@ -6069,19 +6128,21 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
       <c r="Z67" s="8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AA67" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB67" s="7"/>
+      <c r="AB67" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:28">
       <c r="A68" s="3">
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026040916</v>
+        <v>2026041102</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -6090,44 +6151,38 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>75</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
       <c r="L68" s="6" t="s">
-        <v>260</v>
+        <v>121</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P68" s="3"/>
-      <c r="Q68" s="3">
-        <v>1500</v>
-      </c>
+      <c r="Q68" s="3"/>
       <c r="R68" s="3">
-        <v>22500</v>
+        <v>0</v>
       </c>
       <c r="S68" s="3" t="s">
         <v>41</v>
@@ -6137,11 +6192,9 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
-      <c r="Y68" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y68" s="3"/>
       <c r="Z68" s="6" t="s">
-        <v>258</v>
+        <v>126</v>
       </c>
       <c r="AA68" s="3" t="s">
         <v>41</v>
@@ -6155,7 +6208,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026040917</v>
+        <v>2026041056</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -6164,46 +6217,42 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>75</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
       <c r="L69" s="8" t="s">
-        <v>260</v>
+        <v>121</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N69" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P69" s="7"/>
-      <c r="Q69" s="7">
-        <v>1500</v>
-      </c>
+      <c r="Q69" s="7"/>
       <c r="R69" s="7">
-        <v>22500</v>
-      </c>
-      <c r="S69" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
@@ -6211,19 +6260,21 @@
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
       <c r="Z69" s="8" t="s">
-        <v>258</v>
+        <v>126</v>
       </c>
       <c r="AA69" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB69" s="7"/>
+      <c r="AB69" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:28">
       <c r="A70" s="3">
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026040559</v>
+        <v>2026040123</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6232,46 +6283,38 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
       <c r="L70" s="6" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="P70" s="3">
-        <v>451</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>1368</v>
-      </c>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
       <c r="R70" s="3">
-        <v>8005</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>41</v>
@@ -6283,7 +6326,7 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="6" t="s">
-        <v>258</v>
+        <v>126</v>
       </c>
       <c r="AA70" s="3" t="s">
         <v>41</v>
@@ -6297,7 +6340,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026040560</v>
+        <v>2026040806</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -6306,48 +6349,42 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K71" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
       <c r="L71" s="8" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O71" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P71" s="7">
-        <v>451</v>
-      </c>
-      <c r="Q71" s="7">
-        <v>1368</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
       <c r="R71" s="7">
-        <v>8005</v>
-      </c>
-      <c r="S71" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
@@ -6355,19 +6392,21 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
       <c r="Z71" s="8" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="AA71" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB71" s="7"/>
+      <c r="AB71" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:28">
       <c r="A72" s="3">
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026040034</v>
+        <v>2026040557</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6376,19 +6415,19 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>70</v>
+        <v>245</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>35</v>
@@ -6397,25 +6436,29 @@
         <v>36</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P72" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="P72" s="3">
+        <v>2166</v>
+      </c>
       <c r="Q72" s="3">
-        <v>377</v>
+        <v>3083</v>
       </c>
       <c r="R72" s="3">
-        <v>3241</v>
-      </c>
-      <c r="S72" s="3"/>
+        <v>11005</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
@@ -6423,7 +6466,7 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>41</v>
@@ -6437,7 +6480,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026040033</v>
+        <v>2026040558</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6446,19 +6489,19 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>70</v>
+        <v>245</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="J73" s="7" t="s">
         <v>35</v>
@@ -6467,27 +6510,27 @@
         <v>36</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="O73" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="P73" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="P73" s="7">
+        <v>2166</v>
+      </c>
       <c r="Q73" s="7">
-        <v>377</v>
+        <v>3083</v>
       </c>
       <c r="R73" s="7">
-        <v>3241</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>11005</v>
+      </c>
+      <c r="S73" s="7"/>
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
@@ -6495,7 +6538,7 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA73" s="7" t="s">
         <v>41</v>
@@ -6507,7 +6550,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026040434</v>
+        <v>2026040916</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6516,19 +6559,19 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>267</v>
+        <v>70</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>35</v>
@@ -6537,37 +6580,37 @@
         <v>36</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>37</v>
+        <v>280</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P74" s="3"/>
       <c r="Q74" s="3">
-        <v>377</v>
+        <v>1500</v>
       </c>
       <c r="R74" s="3">
-        <v>3241</v>
-      </c>
-      <c r="S74" s="3"/>
+        <v>22500</v>
+      </c>
+      <c r="S74" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
-      <c r="W74" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="W74" s="3"/>
       <c r="X74" s="3"/>
       <c r="Y74" s="3" t="s">
         <v>41</v>
       </c>
       <c r="Z74" s="6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AA74" s="3" t="s">
         <v>41</v>
@@ -6581,7 +6624,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="7">
-        <v>2026040914</v>
+        <v>2026040917</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -6590,46 +6633,46 @@
         <v>29</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>75</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>267</v>
+        <v>70</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K75" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="O75" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P75" s="7"/>
-      <c r="Q75" s="7"/>
+      <c r="Q75" s="7">
+        <v>1500</v>
+      </c>
       <c r="R75" s="7">
-        <v>53451</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>22500</v>
+      </c>
+      <c r="S75" s="7"/>
       <c r="T75" s="7"/>
       <c r="U75" s="7"/>
       <c r="V75" s="7"/>
@@ -6637,21 +6680,19 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
       <c r="Z75" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA75" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB75" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB75" s="7"/>
     </row>
     <row r="76" spans="1:28">
       <c r="A76" s="3">
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>2026040915</v>
+        <v>2026040559</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -6660,44 +6701,50 @@
         <v>29</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>70</v>
+        <v>283</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="P76" s="3">
+        <v>451</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>1368</v>
+      </c>
       <c r="R76" s="3">
-        <v>53451</v>
-      </c>
-      <c r="S76" s="3"/>
+        <v>8005</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
@@ -6705,19 +6752,21 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB76" s="3"/>
+      <c r="AB76" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:28">
       <c r="A77" s="7">
         <v>75</v>
       </c>
       <c r="B77" s="7">
-        <v>2026040832</v>
+        <v>2026040560</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
@@ -6726,42 +6775,46 @@
         <v>29</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K77" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="O77" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P77" s="7"/>
-      <c r="Q77" s="7"/>
+      <c r="P77" s="7">
+        <v>451</v>
+      </c>
+      <c r="Q77" s="7">
+        <v>1368</v>
+      </c>
       <c r="R77" s="7">
-        <v>86361</v>
+        <v>8005</v>
       </c>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
@@ -6771,21 +6824,19 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA77" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB77" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB77" s="7"/>
     </row>
     <row r="78" spans="1:28">
       <c r="A78" s="3">
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>2026040831</v>
+        <v>2026040033</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -6794,42 +6845,44 @@
         <v>29</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>45</v>
       </c>
       <c r="P78" s="3"/>
-      <c r="Q78" s="3"/>
+      <c r="Q78" s="3">
+        <v>377</v>
+      </c>
       <c r="R78" s="3">
-        <v>86361</v>
+        <v>3241</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>41</v>
@@ -6841,19 +6894,21 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA78" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB78" s="3"/>
+      <c r="AB78" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:28">
       <c r="A79" s="7">
         <v>77</v>
       </c>
       <c r="B79" s="7">
-        <v>2026040038</v>
+        <v>2026040034</v>
       </c>
       <c r="C79" s="7">
         <v>1</v>
@@ -6862,46 +6917,46 @@
         <v>29</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G79" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="H79" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H79" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="I79" s="7" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="K79" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>278</v>
+        <v>37</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O79" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P79" s="7"/>
-      <c r="Q79" s="7"/>
+      <c r="Q79" s="7">
+        <v>377</v>
+      </c>
       <c r="R79" s="7">
-        <v>185800</v>
-      </c>
-      <c r="S79" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>3241</v>
+      </c>
+      <c r="S79" s="7"/>
       <c r="T79" s="7"/>
       <c r="U79" s="7"/>
       <c r="V79" s="7"/>
@@ -6909,21 +6964,19 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA79" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB79" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB79" s="7"/>
     </row>
     <row r="80" spans="1:28">
       <c r="A80" s="3">
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>2026040039</v>
+        <v>2026040434</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -6932,64 +6985,72 @@
         <v>29</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G80" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H80" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="I80" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>278</v>
+        <v>37</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P80" s="3"/>
-      <c r="Q80" s="3"/>
+      <c r="Q80" s="3">
+        <v>377</v>
+      </c>
       <c r="R80" s="3">
-        <v>185800</v>
+        <v>3241</v>
       </c>
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
-      <c r="W80" s="3"/>
+      <c r="W80" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
+      <c r="Y80" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z80" s="6" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="AA80" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB80" s="3"/>
+      <c r="AB80" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" spans="1:28">
       <c r="A81" s="7">
         <v>79</v>
       </c>
       <c r="B81" s="7">
-        <v>2026040040</v>
+        <v>2026040914</v>
       </c>
       <c r="C81" s="7">
         <v>1</v>
@@ -6998,34 +7059,34 @@
         <v>29</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K81" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>45</v>
@@ -7033,7 +7094,7 @@
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
       <c r="R81" s="7">
-        <v>187678</v>
+        <v>53451</v>
       </c>
       <c r="S81" s="7" t="s">
         <v>41</v>
@@ -7045,7 +7106,7 @@
       <c r="X81" s="7"/>
       <c r="Y81" s="7"/>
       <c r="Z81" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA81" s="7" t="s">
         <v>41</v>
@@ -7059,7 +7120,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>2026040041</v>
+        <v>2026040915</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
@@ -7068,34 +7129,34 @@
         <v>29</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>40</v>
@@ -7103,7 +7164,7 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3">
-        <v>187678</v>
+        <v>53451</v>
       </c>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
@@ -7113,7 +7174,7 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA82" s="3" t="s">
         <v>41</v>
@@ -7125,7 +7186,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="7">
-        <v>2026041044</v>
+        <v>2026040831</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
@@ -7134,40 +7195,42 @@
         <v>29</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="N83" s="8"/>
+        <v>295</v>
+      </c>
+      <c r="N83" s="8" t="s">
+        <v>296</v>
+      </c>
       <c r="O83" s="7" t="s">
         <v>45</v>
       </c>
       <c r="P83" s="7"/>
       <c r="Q83" s="7"/>
       <c r="R83" s="7">
-        <v>62000</v>
+        <v>86361</v>
       </c>
       <c r="S83" s="7" t="s">
         <v>41</v>
@@ -7179,7 +7242,7 @@
       <c r="X83" s="7"/>
       <c r="Y83" s="7"/>
       <c r="Z83" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA83" s="7" t="s">
         <v>41</v>
@@ -7193,7 +7256,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>2026041045</v>
+        <v>2026040832</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
@@ -7202,40 +7265,42 @@
         <v>29</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="N84" s="6"/>
+        <v>295</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>296</v>
+      </c>
       <c r="O84" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
       <c r="R84" s="3">
-        <v>62000</v>
+        <v>86361</v>
       </c>
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
@@ -7245,7 +7310,7 @@
       <c r="X84" s="3"/>
       <c r="Y84" s="3"/>
       <c r="Z84" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA84" s="3" t="s">
         <v>41</v>
@@ -7257,7 +7322,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="7">
-        <v>2026040830</v>
+        <v>2026040038</v>
       </c>
       <c r="C85" s="7">
         <v>1</v>
@@ -7266,19 +7331,19 @@
         <v>29</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="J85" s="7" t="s">
         <v>77</v>
@@ -7287,23 +7352,25 @@
         <v>36</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>181</v>
+        <v>298</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="O85" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P85" s="7"/>
       <c r="Q85" s="7"/>
       <c r="R85" s="7">
-        <v>6841</v>
-      </c>
-      <c r="S85" s="7"/>
+        <v>185800</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T85" s="7"/>
       <c r="U85" s="7"/>
       <c r="V85" s="7"/>
@@ -7311,7 +7378,7 @@
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
       <c r="Z85" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA85" s="7" t="s">
         <v>41</v>
@@ -7325,7 +7392,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>2026040829</v>
+        <v>2026040039</v>
       </c>
       <c r="C86" s="3">
         <v>1</v>
@@ -7334,19 +7401,19 @@
         <v>29</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>77</v>
@@ -7355,25 +7422,23 @@
         <v>36</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>181</v>
+        <v>298</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
       <c r="R86" s="3">
-        <v>6841</v>
-      </c>
-      <c r="S86" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>185800</v>
+      </c>
+      <c r="S86" s="3"/>
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
@@ -7381,7 +7446,7 @@
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
       <c r="Z86" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA86" s="3" t="s">
         <v>41</v>
@@ -7393,7 +7458,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="7">
-        <v>2026040151</v>
+        <v>2026040040</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -7402,34 +7467,34 @@
         <v>29</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>289</v>
+        <v>117</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="K87" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="N87" s="8" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>45</v>
@@ -7437,7 +7502,7 @@
       <c r="P87" s="7"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="7">
-        <v>120858</v>
+        <v>187678</v>
       </c>
       <c r="S87" s="7" t="s">
         <v>41</v>
@@ -7449,17 +7514,21 @@
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
       <c r="Z87" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA87" s="7"/>
-      <c r="AB87" s="7"/>
+        <v>278</v>
+      </c>
+      <c r="AA87" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB87" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:28">
       <c r="A88" s="3">
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>2026040152</v>
+        <v>2026040041</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -7468,34 +7537,34 @@
         <v>29</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>289</v>
+        <v>117</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="O88" s="3" t="s">
         <v>40</v>
@@ -7503,7 +7572,7 @@
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3">
-        <v>120858</v>
+        <v>187678</v>
       </c>
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
@@ -7513,7 +7582,7 @@
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
       <c r="Z88" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA88" s="3" t="s">
         <v>41</v>
@@ -7525,7 +7594,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="7">
-        <v>2026040439</v>
+        <v>2026041044</v>
       </c>
       <c r="C89" s="7">
         <v>1</v>
@@ -7534,44 +7603,40 @@
         <v>29</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="N89" s="8" t="s">
-        <v>262</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N89" s="8"/>
       <c r="O89" s="7" t="s">
         <v>45</v>
       </c>
       <c r="P89" s="7"/>
-      <c r="Q89" s="7">
-        <v>27727</v>
-      </c>
+      <c r="Q89" s="7"/>
       <c r="R89" s="7">
-        <v>47856</v>
+        <v>62000</v>
       </c>
       <c r="S89" s="7" t="s">
         <v>41</v>
@@ -7583,17 +7648,21 @@
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
       <c r="Z89" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA89" s="7"/>
-      <c r="AB89" s="7"/>
+        <v>278</v>
+      </c>
+      <c r="AA89" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB89" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:28">
       <c r="A90" s="3">
         <v>88</v>
       </c>
       <c r="B90" s="3">
-        <v>2026040440</v>
+        <v>2026041045</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
@@ -7602,44 +7671,40 @@
         <v>29</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>262</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N90" s="6"/>
       <c r="O90" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P90" s="3"/>
-      <c r="Q90" s="3">
-        <v>27727</v>
-      </c>
+      <c r="Q90" s="3"/>
       <c r="R90" s="3">
-        <v>47856</v>
+        <v>62000</v>
       </c>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
@@ -7649,7 +7714,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA90" s="3" t="s">
         <v>41</v>
@@ -7661,7 +7726,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="7">
-        <v>2026040481</v>
+        <v>2026040829</v>
       </c>
       <c r="C91" s="7">
         <v>1</v>
@@ -7670,34 +7735,34 @@
         <v>29</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="K91" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>298</v>
+        <v>187</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="O91" s="7" t="s">
         <v>45</v>
@@ -7705,7 +7770,7 @@
       <c r="P91" s="7"/>
       <c r="Q91" s="7"/>
       <c r="R91" s="7">
-        <v>26583</v>
+        <v>6841</v>
       </c>
       <c r="S91" s="7" t="s">
         <v>41</v>
@@ -7717,17 +7782,21 @@
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
       <c r="Z91" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA91" s="7"/>
-      <c r="AB91" s="7"/>
+        <v>278</v>
+      </c>
+      <c r="AA91" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB91" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:28">
       <c r="A92" s="3">
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>2026040482</v>
+        <v>2026040830</v>
       </c>
       <c r="C92" s="3">
         <v>1</v>
@@ -7736,34 +7805,34 @@
         <v>29</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>298</v>
+        <v>187</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="O92" s="3" t="s">
         <v>40</v>
@@ -7771,7 +7840,7 @@
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
       <c r="R92" s="3">
-        <v>26583</v>
+        <v>6841</v>
       </c>
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
@@ -7781,7 +7850,7 @@
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
       <c r="Z92" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA92" s="3" t="s">
         <v>41</v>
@@ -7793,7 +7862,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="7">
-        <v>2026040141</v>
+        <v>2026040151</v>
       </c>
       <c r="C93" s="7">
         <v>1</v>
@@ -7802,34 +7871,34 @@
         <v>29</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K93" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="O93" s="7" t="s">
         <v>45</v>
@@ -7837,7 +7906,7 @@
       <c r="P93" s="7"/>
       <c r="Q93" s="7"/>
       <c r="R93" s="7">
-        <v>16836</v>
+        <v>120858</v>
       </c>
       <c r="S93" s="7" t="s">
         <v>41</v>
@@ -7849,7 +7918,7 @@
       <c r="X93" s="7"/>
       <c r="Y93" s="7"/>
       <c r="Z93" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA93" s="7"/>
       <c r="AB93" s="7"/>
@@ -7859,7 +7928,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>2026040142</v>
+        <v>2026040152</v>
       </c>
       <c r="C94" s="3">
         <v>1</v>
@@ -7868,34 +7937,34 @@
         <v>29</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>40</v>
@@ -7903,7 +7972,7 @@
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3">
-        <v>16836</v>
+        <v>120858</v>
       </c>
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
@@ -7913,7 +7982,7 @@
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
       <c r="Z94" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>41</v>
@@ -7925,7 +7994,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="7">
-        <v>2026040143</v>
+        <v>2026040439</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
@@ -7934,42 +8003,44 @@
         <v>29</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="K95" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="O95" s="7" t="s">
         <v>45</v>
       </c>
       <c r="P95" s="7"/>
-      <c r="Q95" s="7"/>
+      <c r="Q95" s="7">
+        <v>27727</v>
+      </c>
       <c r="R95" s="7">
-        <v>69969</v>
+        <v>47856</v>
       </c>
       <c r="S95" s="7" t="s">
         <v>41</v>
@@ -7981,7 +8052,7 @@
       <c r="X95" s="7"/>
       <c r="Y95" s="7"/>
       <c r="Z95" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA95" s="7"/>
       <c r="AB95" s="7"/>
@@ -7991,7 +8062,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="3">
-        <v>2026040144</v>
+        <v>2026040440</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -8000,42 +8071,44 @@
         <v>29</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P96" s="3"/>
-      <c r="Q96" s="3"/>
+      <c r="Q96" s="3">
+        <v>27727</v>
+      </c>
       <c r="R96" s="3">
-        <v>69969</v>
+        <v>47856</v>
       </c>
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
@@ -8045,7 +8118,7 @@
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
       <c r="Z96" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA96" s="3" t="s">
         <v>41</v>
@@ -8057,7 +8130,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="7">
-        <v>2026040149</v>
+        <v>2026040482</v>
       </c>
       <c r="C97" s="7">
         <v>1</v>
@@ -8066,46 +8139,44 @@
         <v>29</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K97" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="M97" s="8" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="N97" s="8" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="O97" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P97" s="7"/>
       <c r="Q97" s="7"/>
       <c r="R97" s="7">
-        <v>155088</v>
-      </c>
-      <c r="S97" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>26583</v>
+      </c>
+      <c r="S97" s="7"/>
       <c r="T97" s="7"/>
       <c r="U97" s="7"/>
       <c r="V97" s="7"/>
@@ -8113,17 +8184,21 @@
       <c r="X97" s="7"/>
       <c r="Y97" s="7"/>
       <c r="Z97" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA97" s="7"/>
-      <c r="AB97" s="7"/>
+        <v>278</v>
+      </c>
+      <c r="AA97" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB97" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" spans="1:28">
       <c r="A98" s="3">
         <v>96</v>
       </c>
       <c r="B98" s="3">
-        <v>2026040150</v>
+        <v>2026040481</v>
       </c>
       <c r="C98" s="3">
         <v>1</v>
@@ -8132,44 +8207,46 @@
         <v>29</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3">
-        <v>155088</v>
-      </c>
-      <c r="S98" s="3"/>
+        <v>26583</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3"/>
@@ -8177,11 +8254,9 @@
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
       <c r="Z98" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA98" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="AA98" s="3"/>
       <c r="AB98" s="3"/>
     </row>
     <row r="99" spans="1:28">
@@ -8189,7 +8264,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="7">
-        <v>2026040147</v>
+        <v>2026040141</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
@@ -8198,34 +8273,34 @@
         <v>29</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K99" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N99" s="8" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="O99" s="7" t="s">
         <v>45</v>
@@ -8233,7 +8308,7 @@
       <c r="P99" s="7"/>
       <c r="Q99" s="7"/>
       <c r="R99" s="7">
-        <v>116077</v>
+        <v>16836</v>
       </c>
       <c r="S99" s="7" t="s">
         <v>41</v>
@@ -8245,7 +8320,7 @@
       <c r="X99" s="7"/>
       <c r="Y99" s="7"/>
       <c r="Z99" s="8" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA99" s="7"/>
       <c r="AB99" s="7"/>
@@ -8255,7 +8330,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="3">
-        <v>2026040148</v>
+        <v>2026040142</v>
       </c>
       <c r="C100" s="3">
         <v>1</v>
@@ -8264,34 +8339,34 @@
         <v>29</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>40</v>
@@ -8299,7 +8374,7 @@
       <c r="P100" s="3"/>
       <c r="Q100" s="3"/>
       <c r="R100" s="3">
-        <v>116077</v>
+        <v>16836</v>
       </c>
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
@@ -8309,7 +8384,7 @@
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
       <c r="Z100" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>41</v>
@@ -8321,7 +8396,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="7">
-        <v>2026040099</v>
+        <v>2026040143</v>
       </c>
       <c r="C101" s="7">
         <v>1</v>
@@ -8330,44 +8405,46 @@
         <v>29</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="O101" s="7" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P101" s="7"/>
       <c r="Q101" s="7"/>
       <c r="R101" s="7">
-        <v>0</v>
-      </c>
-      <c r="S101" s="7"/>
+        <v>69969</v>
+      </c>
+      <c r="S101" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T101" s="7"/>
       <c r="U101" s="7"/>
       <c r="V101" s="7"/>
@@ -8375,21 +8452,17 @@
       <c r="X101" s="7"/>
       <c r="Y101" s="7"/>
       <c r="Z101" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="AA101" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB101" s="7">
-        <v>1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="AA101" s="7"/>
+      <c r="AB101" s="7"/>
     </row>
     <row r="102" spans="1:28">
       <c r="A102" s="3">
         <v>100</v>
       </c>
       <c r="B102" s="3">
-        <v>2026040195</v>
+        <v>2026040144</v>
       </c>
       <c r="C102" s="3">
         <v>1</v>
@@ -8398,66 +8471,64 @@
         <v>29</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>318</v>
+        <v>62</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
+        <v>324</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L102" s="6" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3"/>
       <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>69969</v>
+      </c>
+      <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
-      <c r="Y102" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y102" s="3"/>
       <c r="Z102" s="6" t="s">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB102" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB102" s="3"/>
     </row>
     <row r="103" spans="1:28">
       <c r="A103" s="7">
         <v>101</v>
       </c>
       <c r="B103" s="7">
-        <v>2026040050</v>
+        <v>2026040149</v>
       </c>
       <c r="C103" s="7">
         <v>1</v>
@@ -8466,30 +8537,34 @@
         <v>29</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>289</v>
+        <v>129</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="J103" s="7"/>
-      <c r="K103" s="7"/>
+        <v>327</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L103" s="8" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="O103" s="7" t="s">
         <v>45</v>
@@ -8497,37 +8572,29 @@
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
       <c r="R103" s="7">
-        <v>0</v>
+        <v>155088</v>
       </c>
       <c r="S103" s="7" t="s">
         <v>41</v>
       </c>
       <c r="T103" s="7"/>
-      <c r="U103" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U103" s="7"/>
       <c r="V103" s="7"/>
       <c r="W103" s="7"/>
       <c r="X103" s="7"/>
-      <c r="Y103" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y103" s="7"/>
       <c r="Z103" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA103" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB103" s="7">
-        <v>1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="AA103" s="7"/>
+      <c r="AB103" s="7"/>
     </row>
     <row r="104" spans="1:28">
       <c r="A104" s="3">
         <v>102</v>
       </c>
       <c r="B104" s="3">
-        <v>2026040200</v>
+        <v>2026040150</v>
       </c>
       <c r="C104" s="3">
         <v>1</v>
@@ -8536,42 +8603,42 @@
         <v>29</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
       <c r="R104" s="3">
-        <v>0</v>
+        <v>155088</v>
       </c>
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
@@ -8581,21 +8648,19 @@
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
       <c r="Z104" s="6" t="s">
-        <v>317</v>
+        <v>278</v>
       </c>
       <c r="AA104" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB104" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB104" s="3"/>
     </row>
     <row r="105" spans="1:28">
       <c r="A105" s="7">
         <v>103</v>
       </c>
       <c r="B105" s="7">
-        <v>2026040511</v>
+        <v>2026040147</v>
       </c>
       <c r="C105" s="7">
         <v>1</v>
@@ -8604,30 +8669,34 @@
         <v>29</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>325</v>
+        <v>87</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="J105" s="7"/>
-      <c r="K105" s="7"/>
+        <v>330</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L105" s="8" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="N105" s="8" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="O105" s="7" t="s">
         <v>45</v>
@@ -8635,7 +8704,7 @@
       <c r="P105" s="7"/>
       <c r="Q105" s="7"/>
       <c r="R105" s="7">
-        <v>0</v>
+        <v>116077</v>
       </c>
       <c r="S105" s="7" t="s">
         <v>41</v>
@@ -8645,25 +8714,19 @@
       <c r="V105" s="7"/>
       <c r="W105" s="7"/>
       <c r="X105" s="7"/>
-      <c r="Y105" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y105" s="7"/>
       <c r="Z105" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA105" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB105" s="7">
-        <v>1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="AA105" s="7"/>
+      <c r="AB105" s="7"/>
     </row>
     <row r="106" spans="1:28">
       <c r="A106" s="3">
         <v>104</v>
       </c>
       <c r="B106" s="3">
-        <v>2026040598</v>
+        <v>2026040148</v>
       </c>
       <c r="C106" s="3">
         <v>1</v>
@@ -8672,42 +8735,42 @@
         <v>29</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>118</v>
+        <v>311</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
       <c r="R106" s="3">
-        <v>0</v>
+        <v>116077</v>
       </c>
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
@@ -8717,21 +8780,19 @@
       <c r="X106" s="3"/>
       <c r="Y106" s="3"/>
       <c r="Z106" s="6" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="AA106" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB106" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB106" s="3"/>
     </row>
     <row r="107" spans="1:28">
       <c r="A107" s="7">
         <v>105</v>
       </c>
       <c r="B107" s="7">
-        <v>2026040599</v>
+        <v>2026040099</v>
       </c>
       <c r="C107" s="7">
         <v>1</v>
@@ -8740,37 +8801,37 @@
         <v>29</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M107" s="8" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="N107" s="8" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="O107" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P107" s="7"/>
       <c r="Q107" s="7"/>
@@ -8785,19 +8846,21 @@
       <c r="X107" s="7"/>
       <c r="Y107" s="7"/>
       <c r="Z107" s="8" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AA107" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB107" s="7"/>
+      <c r="AB107" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="108" spans="1:28">
       <c r="A108" s="3">
         <v>106</v>
       </c>
       <c r="B108" s="3">
-        <v>2026040661</v>
+        <v>2026040195</v>
       </c>
       <c r="C108" s="3">
         <v>1</v>
@@ -8806,30 +8869,30 @@
         <v>29</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>145</v>
+        <v>337</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
       <c r="L108" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="O108" s="3" t="s">
         <v>45</v>
@@ -8839,29 +8902,33 @@
       <c r="R108" s="3">
         <v>0</v>
       </c>
-      <c r="S108" s="3"/>
-      <c r="T108" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S108" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T108" s="3"/>
       <c r="U108" s="3"/>
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
-      <c r="Y108" s="3"/>
+      <c r="Y108" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z108" s="6" t="s">
-        <v>330</v>
+        <v>126</v>
       </c>
       <c r="AA108" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB108" s="3"/>
+      <c r="AB108" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="109" spans="1:28">
       <c r="A109" s="7">
         <v>107</v>
       </c>
       <c r="B109" s="7">
-        <v>2026040585</v>
+        <v>2026040050</v>
       </c>
       <c r="C109" s="7">
         <v>1</v>
@@ -8870,52 +8937,54 @@
         <v>29</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>331</v>
+        <v>31</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="J109" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="K109" s="7" t="s">
-        <v>117</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
       <c r="L109" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M109" s="8" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="N109" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="O109" s="7" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P109" s="7"/>
       <c r="Q109" s="7"/>
       <c r="R109" s="7">
         <v>0</v>
       </c>
-      <c r="S109" s="7"/>
+      <c r="S109" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T109" s="7"/>
-      <c r="U109" s="7"/>
+      <c r="U109" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V109" s="7"/>
       <c r="W109" s="7"/>
       <c r="X109" s="7"/>
-      <c r="Y109" s="7"/>
+      <c r="Y109" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z109" s="8" t="s">
-        <v>336</v>
+        <v>126</v>
       </c>
       <c r="AA109" s="7" t="s">
         <v>41</v>
@@ -8929,7 +8998,7 @@
         <v>108</v>
       </c>
       <c r="B110" s="3">
-        <v>2026040907</v>
+        <v>2026040200</v>
       </c>
       <c r="C110" s="3">
         <v>1</v>
@@ -8938,37 +9007,37 @@
         <v>29</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>289</v>
+        <v>129</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
@@ -8983,7 +9052,7 @@
       <c r="X110" s="3"/>
       <c r="Y110" s="3"/>
       <c r="Z110" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AA110" s="3" t="s">
         <v>41</v>
@@ -8997,7 +9066,7 @@
         <v>109</v>
       </c>
       <c r="B111" s="7">
-        <v>2026041049</v>
+        <v>2026040511</v>
       </c>
       <c r="C111" s="7">
         <v>1</v>
@@ -9006,30 +9075,30 @@
         <v>29</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>289</v>
+        <v>129</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M111" s="8" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O111" s="7" t="s">
         <v>45</v>
@@ -9051,7 +9120,7 @@
         <v>41</v>
       </c>
       <c r="Z111" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AA111" s="7" t="s">
         <v>41</v>
@@ -9065,7 +9134,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="3">
-        <v>2026040469</v>
+        <v>2026040598</v>
       </c>
       <c r="C112" s="3">
         <v>1</v>
@@ -9074,52 +9143,52 @@
         <v>29</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>341</v>
+        <v>69</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="J112" s="3"/>
-      <c r="K112" s="3"/>
+        <v>344</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="L112" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="P112" s="3"/>
       <c r="Q112" s="3"/>
       <c r="R112" s="3">
         <v>0</v>
       </c>
-      <c r="S112" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
-      <c r="Y112" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y112" s="3"/>
       <c r="Z112" s="6" t="s">
-        <v>123</v>
+        <v>347</v>
       </c>
       <c r="AA112" s="3" t="s">
         <v>41</v>
@@ -9133,7 +9202,7 @@
         <v>111</v>
       </c>
       <c r="B113" s="7">
-        <v>2026040209</v>
+        <v>2026040599</v>
       </c>
       <c r="C113" s="7">
         <v>1</v>
@@ -9142,37 +9211,37 @@
         <v>29</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>341</v>
+        <v>69</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M113" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O113" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P113" s="7"/>
       <c r="Q113" s="7"/>
@@ -9187,7 +9256,7 @@
       <c r="X113" s="7"/>
       <c r="Y113" s="7"/>
       <c r="Z113" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA113" s="7" t="s">
         <v>41</v>
@@ -9199,7 +9268,7 @@
         <v>112</v>
       </c>
       <c r="B114" s="3">
-        <v>2026040788</v>
+        <v>2026040661</v>
       </c>
       <c r="C114" s="3">
         <v>1</v>
@@ -9208,34 +9277,30 @@
         <v>29</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>307</v>
+        <v>151</v>
       </c>
       <c r="I114" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N114" s="6" t="s">
         <v>346</v>
-      </c>
-      <c r="J114" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="K114" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="L114" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="O114" s="3" t="s">
         <v>45</v>
@@ -9246,30 +9311,28 @@
         <v>0</v>
       </c>
       <c r="S114" s="3"/>
-      <c r="T114" s="3"/>
+      <c r="T114" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="U114" s="3"/>
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
-      <c r="Y114" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y114" s="3"/>
       <c r="Z114" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AA114" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB114" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB114" s="3"/>
     </row>
     <row r="115" spans="1:28">
       <c r="A115" s="7">
         <v>113</v>
       </c>
       <c r="B115" s="7">
-        <v>2026040430</v>
+        <v>2026041138</v>
       </c>
       <c r="C115" s="7">
         <v>1</v>
@@ -9278,52 +9341,52 @@
         <v>29</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>353</v>
+        <v>274</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>354</v>
+        <v>87</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="K115" s="7" t="s">
-        <v>117</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="J115" s="7"/>
+      <c r="K115" s="7"/>
       <c r="L115" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="N115" s="8" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="O115" s="7" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="P115" s="7"/>
       <c r="Q115" s="7"/>
       <c r="R115" s="7">
         <v>0</v>
       </c>
-      <c r="S115" s="7"/>
+      <c r="S115" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T115" s="7"/>
       <c r="U115" s="7"/>
       <c r="V115" s="7"/>
       <c r="W115" s="7"/>
       <c r="X115" s="7"/>
-      <c r="Y115" s="7"/>
+      <c r="Y115" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z115" s="8" t="s">
-        <v>358</v>
+        <v>126</v>
       </c>
       <c r="AA115" s="7" t="s">
         <v>41</v>
@@ -9337,7 +9400,7 @@
         <v>114</v>
       </c>
       <c r="B116" s="3">
-        <v>2026040568</v>
+        <v>2026041061</v>
       </c>
       <c r="C116" s="3">
         <v>1</v>
@@ -9346,37 +9409,37 @@
         <v>29</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>353</v>
+        <v>274</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>75</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P116" s="3"/>
       <c r="Q116" s="3"/>
@@ -9391,21 +9454,19 @@
       <c r="X116" s="3"/>
       <c r="Y116" s="3"/>
       <c r="Z116" s="6" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="AA116" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB116" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB116" s="3"/>
     </row>
     <row r="117" spans="1:28">
       <c r="A117" s="7">
         <v>115</v>
       </c>
       <c r="B117" s="7">
-        <v>2026041055</v>
+        <v>2026040585</v>
       </c>
       <c r="C117" s="7">
         <v>1</v>
@@ -9414,42 +9475,44 @@
         <v>29</v>
       </c>
       <c r="E117" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F117" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="G117" s="7" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>363</v>
+        <v>211</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="J117" s="7"/>
-      <c r="K117" s="7"/>
+        <v>354</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="K117" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="L117" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="N117" s="8" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="O117" s="7" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="P117" s="7"/>
       <c r="Q117" s="7"/>
       <c r="R117" s="7">
         <v>0</v>
       </c>
-      <c r="S117" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="S117" s="7"/>
       <c r="T117" s="7"/>
       <c r="U117" s="7"/>
       <c r="V117" s="7"/>
@@ -9457,45 +9520,657 @@
       <c r="X117" s="7"/>
       <c r="Y117" s="7"/>
       <c r="Z117" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA117" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB117" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28">
+      <c r="A118" s="3">
+        <v>116</v>
+      </c>
+      <c r="B118" s="3">
+        <v>2026040907</v>
+      </c>
+      <c r="C118" s="3">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L118" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M118" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="N118" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P118" s="3"/>
+      <c r="Q118" s="3"/>
+      <c r="R118" s="3">
+        <v>0</v>
+      </c>
+      <c r="S118" s="3"/>
+      <c r="T118" s="3"/>
+      <c r="U118" s="3"/>
+      <c r="V118" s="3"/>
+      <c r="W118" s="3"/>
+      <c r="X118" s="3"/>
+      <c r="Y118" s="3"/>
+      <c r="Z118" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="AA118" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB118" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28">
+      <c r="A119" s="7">
+        <v>117</v>
+      </c>
+      <c r="B119" s="7">
+        <v>2026041049</v>
+      </c>
+      <c r="C119" s="7">
+        <v>1</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="J119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M119" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="N119" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="O119" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7">
+        <v>0</v>
+      </c>
+      <c r="S119" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T119" s="7"/>
+      <c r="U119" s="7"/>
+      <c r="V119" s="7"/>
+      <c r="W119" s="7"/>
+      <c r="X119" s="7"/>
+      <c r="Y119" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z119" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA119" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB119" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28">
+      <c r="A120" s="3">
+        <v>118</v>
+      </c>
+      <c r="B120" s="3">
+        <v>2026040469</v>
+      </c>
+      <c r="C120" s="3">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P120" s="3"/>
+      <c r="Q120" s="3"/>
+      <c r="R120" s="3">
+        <v>0</v>
+      </c>
+      <c r="S120" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T120" s="3"/>
+      <c r="U120" s="3"/>
+      <c r="V120" s="3"/>
+      <c r="W120" s="3"/>
+      <c r="X120" s="3"/>
+      <c r="Y120" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z120" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA120" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB120" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28">
+      <c r="A121" s="7">
+        <v>119</v>
+      </c>
+      <c r="B121" s="7">
+        <v>2026040209</v>
+      </c>
+      <c r="C121" s="7">
+        <v>1</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="J121" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="L121" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M121" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="N121" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="O121" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="P121" s="7"/>
+      <c r="Q121" s="7"/>
+      <c r="R121" s="7">
+        <v>0</v>
+      </c>
+      <c r="S121" s="7"/>
+      <c r="T121" s="7"/>
+      <c r="U121" s="7"/>
+      <c r="V121" s="7"/>
+      <c r="W121" s="7"/>
+      <c r="X121" s="7"/>
+      <c r="Y121" s="7"/>
+      <c r="Z121" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="AA121" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB121" s="7"/>
+    </row>
+    <row r="122" spans="1:28">
+      <c r="A122" s="3">
+        <v>120</v>
+      </c>
+      <c r="B122" s="3">
+        <v>2026040788</v>
+      </c>
+      <c r="C122" s="3">
+        <v>1</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K122" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="L122" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="N122" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P122" s="3"/>
+      <c r="Q122" s="3"/>
+      <c r="R122" s="3">
+        <v>0</v>
+      </c>
+      <c r="S122" s="3"/>
+      <c r="T122" s="3"/>
+      <c r="U122" s="3"/>
+      <c r="V122" s="3"/>
+      <c r="W122" s="3"/>
+      <c r="X122" s="3"/>
+      <c r="Y122" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z122" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="AA122" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB122" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28">
+      <c r="A123" s="7">
+        <v>121</v>
+      </c>
+      <c r="B123" s="7">
+        <v>2026041181</v>
+      </c>
+      <c r="C123" s="7">
+        <v>1</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="J123" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="K123" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="L123" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="M123" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="N123" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="O123" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P123" s="7"/>
+      <c r="Q123" s="7"/>
+      <c r="R123" s="7">
+        <v>0</v>
+      </c>
+      <c r="S123" s="7"/>
+      <c r="T123" s="7"/>
+      <c r="U123" s="7"/>
+      <c r="V123" s="7"/>
+      <c r="W123" s="7"/>
+      <c r="X123" s="7"/>
+      <c r="Y123" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z123" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA123" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB123" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28">
+      <c r="A124" s="3">
+        <v>122</v>
+      </c>
+      <c r="B124" s="3">
+        <v>2026040430</v>
+      </c>
+      <c r="C124" s="3">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L124" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M124" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="N124" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P124" s="3"/>
+      <c r="Q124" s="3"/>
+      <c r="R124" s="3">
+        <v>0</v>
+      </c>
+      <c r="S124" s="3"/>
+      <c r="T124" s="3"/>
+      <c r="U124" s="3"/>
+      <c r="V124" s="3"/>
+      <c r="W124" s="3"/>
+      <c r="X124" s="3"/>
+      <c r="Y124" s="3"/>
+      <c r="Z124" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="AA124" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB124" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28">
+      <c r="A125" s="7">
         <v>123</v>
       </c>
-      <c r="AA117" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB117" s="7"/>
-    </row>
-    <row r="118" spans="1:28">
-      <c r="A118" s="9"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
-      <c r="I118" s="9"/>
-      <c r="J118" s="9"/>
-      <c r="K118" s="9"/>
-      <c r="L118" s="10"/>
-      <c r="M118" s="10"/>
-      <c r="N118" s="10"/>
-      <c r="O118" s="9"/>
-      <c r="P118" s="9"/>
-      <c r="Q118" s="9"/>
-      <c r="R118" s="9"/>
-      <c r="S118" s="9"/>
-      <c r="T118" s="9"/>
-      <c r="U118" s="9"/>
-      <c r="V118" s="9"/>
-      <c r="W118" s="9"/>
-      <c r="X118" s="9"/>
-      <c r="Y118" s="9"/>
-      <c r="Z118" s="10"/>
-      <c r="AA118" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="AB118" s="9">
-        <v>63</v>
+      <c r="B125" s="7">
+        <v>2026041055</v>
+      </c>
+      <c r="C125" s="7">
+        <v>1</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="I125" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="J125" s="7"/>
+      <c r="K125" s="7"/>
+      <c r="L125" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M125" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="N125" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="O125" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P125" s="7"/>
+      <c r="Q125" s="7"/>
+      <c r="R125" s="7">
+        <v>0</v>
+      </c>
+      <c r="S125" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T125" s="7"/>
+      <c r="U125" s="7"/>
+      <c r="V125" s="7"/>
+      <c r="W125" s="7"/>
+      <c r="X125" s="7"/>
+      <c r="Y125" s="7"/>
+      <c r="Z125" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA125" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB125" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28">
+      <c r="A126" s="3">
+        <v>124</v>
+      </c>
+      <c r="B126" s="3">
+        <v>2026040568</v>
+      </c>
+      <c r="C126" s="3">
+        <v>1</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L126" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="N126" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="O126" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P126" s="3"/>
+      <c r="Q126" s="3"/>
+      <c r="R126" s="3">
+        <v>0</v>
+      </c>
+      <c r="S126" s="3"/>
+      <c r="T126" s="3"/>
+      <c r="U126" s="3"/>
+      <c r="V126" s="3"/>
+      <c r="W126" s="3"/>
+      <c r="X126" s="3"/>
+      <c r="Y126" s="3"/>
+      <c r="Z126" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="AA126" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB126" s="3"/>
+    </row>
+    <row r="127" spans="1:28">
+      <c r="A127" s="9"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="9"/>
+      <c r="H127" s="9"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="9"/>
+      <c r="K127" s="9"/>
+      <c r="L127" s="10"/>
+      <c r="M127" s="10"/>
+      <c r="N127" s="10"/>
+      <c r="O127" s="9"/>
+      <c r="P127" s="9"/>
+      <c r="Q127" s="9"/>
+      <c r="R127" s="9"/>
+      <c r="S127" s="9"/>
+      <c r="T127" s="9"/>
+      <c r="U127" s="9"/>
+      <c r="V127" s="9"/>
+      <c r="W127" s="9"/>
+      <c r="X127" s="9"/>
+      <c r="Y127" s="9"/>
+      <c r="Z127" s="10"/>
+      <c r="AA127" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="AB127" s="9">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202604_Service_Count_Report.xlsx
+++ b/IM/202604_Service_Count_Report.xlsx
@@ -1311,6 +1311,9 @@
 將執行不備份更換硬碟</t>
   </si>
   <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
     <t>14:57:00</t>
   </si>
   <si>
@@ -1318,9 +1321,6 @@
  更換Tm2 一二顆硬碟不備份還原最新母版 
 TM TCx800 S0902 42 0 
 HiPOS 最新版本 S0409 61 0 ARC DEF 5 408u 已跟店家告知回報代收會計</t>
-  </si>
-  <si>
-    <t>12:30:00</t>
   </si>
   <si>
     <t>11:26:00</t>
@@ -3500,9 +3500,6 @@
 門市人員測試操作正常</t>
   </si>
   <si>
-    <t>12:28:00</t>
-  </si>
-  <si>
     <t>THILF0D111</t>
   </si>
   <si>
@@ -3515,6 +3512,9 @@
     <t>更換T70
 換上 8138001526
 換下 8138001580</t>
+  </si>
+  <si>
+    <t>12:28:00</t>
   </si>
   <si>
     <t>14:16:00</t>
@@ -5959,7 +5959,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026042651</v>
+        <v>2026042652</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="N30" s="6"/>
       <c r="O30" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3">
@@ -6005,9 +6005,7 @@
       <c r="R30" s="3">
         <v>11713</v>
       </c>
-      <c r="S30" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -6029,7 +6027,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026042652</v>
+        <v>2026042651</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -6066,7 +6064,7 @@
       </c>
       <c r="N31" s="8"/>
       <c r="O31" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7">
@@ -6075,7 +6073,9 @@
       <c r="R31" s="7">
         <v>11713</v>
       </c>
-      <c r="S31" s="7"/>
+      <c r="S31" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -7917,7 +7917,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026042605</v>
+        <v>2026042604</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="N59" s="8"/>
       <c r="O59" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P59" s="7"/>
       <c r="Q59" s="7">
@@ -7963,7 +7963,9 @@
       <c r="R59" s="7">
         <v>27040</v>
       </c>
-      <c r="S59" s="7"/>
+      <c r="S59" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
@@ -7985,7 +7987,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026042604</v>
+        <v>2026042605</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -8022,7 +8024,7 @@
       </c>
       <c r="N60" s="6"/>
       <c r="O60" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P60" s="3"/>
       <c r="Q60" s="3">
@@ -8031,9 +8033,7 @@
       <c r="R60" s="3">
         <v>27040</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S60" s="3"/>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -8053,7 +8053,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026040556</v>
+        <v>2026040555</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -8090,14 +8090,16 @@
       </c>
       <c r="N61" s="8"/>
       <c r="O61" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7">
         <v>127085</v>
       </c>
-      <c r="S61" s="7"/>
+      <c r="S61" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
@@ -8119,7 +8121,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026040555</v>
+        <v>2026040556</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -8156,16 +8158,14 @@
       </c>
       <c r="N62" s="6"/>
       <c r="O62" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3">
         <v>127085</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S62" s="3"/>
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -9519,7 +9519,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="7">
-        <v>2026043846</v>
+        <v>2026043781</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
@@ -9537,13 +9537,17 @@
         <v>256</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="J83" s="7"/>
-      <c r="K83" s="7"/>
+      <c r="J83" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>289</v>
+      </c>
       <c r="L83" s="8" t="s">
         <v>290</v>
       </c>
@@ -9554,26 +9558,22 @@
         <v>299</v>
       </c>
       <c r="O83" s="7" t="s">
-        <v>39</v>
+        <v>230</v>
       </c>
       <c r="P83" s="7"/>
       <c r="Q83" s="7"/>
       <c r="R83" s="7">
         <v>0</v>
       </c>
-      <c r="S83" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S83" s="7"/>
       <c r="T83" s="7"/>
       <c r="U83" s="7"/>
       <c r="V83" s="7"/>
       <c r="W83" s="7"/>
       <c r="X83" s="7"/>
-      <c r="Y83" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y83" s="7"/>
       <c r="Z83" s="8" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AA83" s="7" t="s">
         <v>40</v>
@@ -9585,7 +9585,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>2026043781</v>
+        <v>2026043846</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
@@ -9603,17 +9603,13 @@
         <v>256</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="J84" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>289</v>
-      </c>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
       <c r="L84" s="6" t="s">
         <v>290</v>
       </c>
@@ -9624,22 +9620,26 @@
         <v>299</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>230</v>
+        <v>39</v>
       </c>
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
       <c r="R84" s="3">
         <v>0</v>
       </c>
-      <c r="S84" s="3"/>
+      <c r="S84" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
       <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
+      <c r="Y84" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z84" s="6" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AA84" s="3" t="s">
         <v>40</v>
@@ -12279,10 +12279,10 @@
         <v>122</v>
       </c>
       <c r="B124" s="3">
-        <v>2026042587</v>
+        <v>2026042843</v>
       </c>
       <c r="C124" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>29</v>
@@ -12302,12 +12302,8 @@
       <c r="I124" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="J124" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="K124" s="3" t="s">
-        <v>289</v>
-      </c>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
       <c r="L124" s="6" t="s">
         <v>290</v>
       </c>
@@ -12318,22 +12314,26 @@
         <v>421</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>230</v>
+        <v>39</v>
       </c>
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
       <c r="R124" s="3">
         <v>0</v>
       </c>
-      <c r="S124" s="3"/>
+      <c r="S124" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
-      <c r="Y124" s="3"/>
+      <c r="Y124" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z124" s="6" t="s">
-        <v>424</v>
+        <v>296</v>
       </c>
       <c r="AA124" s="3" t="s">
         <v>40</v>
@@ -12345,10 +12345,10 @@
         <v>123</v>
       </c>
       <c r="B125" s="7">
-        <v>2026042843</v>
+        <v>2026042587</v>
       </c>
       <c r="C125" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>29</v>
@@ -12363,13 +12363,17 @@
         <v>116</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
+      <c r="J125" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="K125" s="7" t="s">
+        <v>289</v>
+      </c>
       <c r="L125" s="8" t="s">
         <v>290</v>
       </c>
@@ -12380,26 +12384,22 @@
         <v>421</v>
       </c>
       <c r="O125" s="7" t="s">
-        <v>39</v>
+        <v>230</v>
       </c>
       <c r="P125" s="7"/>
       <c r="Q125" s="7"/>
       <c r="R125" s="7">
         <v>0</v>
       </c>
-      <c r="S125" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S125" s="7"/>
       <c r="T125" s="7"/>
       <c r="U125" s="7"/>
       <c r="V125" s="7"/>
       <c r="W125" s="7"/>
       <c r="X125" s="7"/>
-      <c r="Y125" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y125" s="7"/>
       <c r="Z125" s="8" t="s">
-        <v>296</v>
+        <v>425</v>
       </c>
       <c r="AA125" s="7" t="s">
         <v>40</v>
@@ -12970,7 +12970,7 @@
         <v>47</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>455</v>
@@ -14937,7 +14937,7 @@
         <v>161</v>
       </c>
       <c r="B163" s="7">
-        <v>2026040499</v>
+        <v>2026040498</v>
       </c>
       <c r="C163" s="7">
         <v>1</v>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="N163" s="8"/>
       <c r="O163" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P163" s="7"/>
       <c r="Q163" s="7">
@@ -14983,9 +14983,13 @@
       <c r="R163" s="7">
         <v>15686</v>
       </c>
-      <c r="S163" s="7"/>
+      <c r="S163" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T163" s="7"/>
-      <c r="U163" s="7"/>
+      <c r="U163" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V163" s="7"/>
       <c r="W163" s="7"/>
       <c r="X163" s="7"/>
@@ -15005,7 +15009,7 @@
         <v>162</v>
       </c>
       <c r="B164" s="3">
-        <v>2026040498</v>
+        <v>2026040499</v>
       </c>
       <c r="C164" s="3">
         <v>1</v>
@@ -15042,7 +15046,7 @@
       </c>
       <c r="N164" s="6"/>
       <c r="O164" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P164" s="3"/>
       <c r="Q164" s="3">
@@ -15051,13 +15055,9 @@
       <c r="R164" s="3">
         <v>15686</v>
       </c>
-      <c r="S164" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S164" s="3"/>
       <c r="T164" s="3"/>
-      <c r="U164" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U164" s="3"/>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
       <c r="X164" s="3"/>
@@ -15409,7 +15409,7 @@
         <v>168</v>
       </c>
       <c r="B170" s="3">
-        <v>2026040109</v>
+        <v>2026040108</v>
       </c>
       <c r="C170" s="3">
         <v>1</v>
@@ -15427,7 +15427,7 @@
         <v>557</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I170" s="3" t="s">
         <v>558</v>
@@ -15448,14 +15448,16 @@
         <v>560</v>
       </c>
       <c r="O170" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P170" s="3"/>
       <c r="Q170" s="3"/>
       <c r="R170" s="3">
         <v>27527</v>
       </c>
-      <c r="S170" s="3"/>
+      <c r="S170" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T170" s="3"/>
       <c r="U170" s="3"/>
       <c r="V170" s="3"/>
@@ -15477,7 +15479,7 @@
         <v>169</v>
       </c>
       <c r="B171" s="7">
-        <v>2026040108</v>
+        <v>2026040109</v>
       </c>
       <c r="C171" s="7">
         <v>1</v>
@@ -15495,7 +15497,7 @@
         <v>557</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>558</v>
@@ -15516,16 +15518,14 @@
         <v>560</v>
       </c>
       <c r="O171" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P171" s="7"/>
       <c r="Q171" s="7"/>
       <c r="R171" s="7">
         <v>27527</v>
       </c>
-      <c r="S171" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S171" s="7"/>
       <c r="T171" s="7"/>
       <c r="U171" s="7"/>
       <c r="V171" s="7"/>
@@ -15739,7 +15739,7 @@
         <v>173</v>
       </c>
       <c r="B175" s="7">
-        <v>2026040463</v>
+        <v>2026040464</v>
       </c>
       <c r="C175" s="7">
         <v>1</v>
@@ -15778,16 +15778,14 @@
         <v>554</v>
       </c>
       <c r="O175" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P175" s="7"/>
       <c r="Q175" s="7"/>
       <c r="R175" s="7">
         <v>92786</v>
       </c>
-      <c r="S175" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S175" s="7"/>
       <c r="T175" s="7"/>
       <c r="U175" s="7"/>
       <c r="V175" s="7"/>
@@ -15805,7 +15803,7 @@
         <v>174</v>
       </c>
       <c r="B176" s="3">
-        <v>2026040464</v>
+        <v>2026040463</v>
       </c>
       <c r="C176" s="3">
         <v>1</v>
@@ -15844,14 +15842,16 @@
         <v>554</v>
       </c>
       <c r="O176" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P176" s="3"/>
       <c r="Q176" s="3"/>
       <c r="R176" s="3">
         <v>92786</v>
       </c>
-      <c r="S176" s="3"/>
+      <c r="S176" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T176" s="3"/>
       <c r="U176" s="3"/>
       <c r="V176" s="3"/>
@@ -16207,7 +16207,7 @@
         <v>180</v>
       </c>
       <c r="B182" s="3">
-        <v>2026040056</v>
+        <v>2026040057</v>
       </c>
       <c r="C182" s="3">
         <v>1</v>
@@ -16246,7 +16246,7 @@
         <v>560</v>
       </c>
       <c r="O182" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P182" s="3"/>
       <c r="Q182" s="3">
@@ -16255,9 +16255,7 @@
       <c r="R182" s="3">
         <v>361051</v>
       </c>
-      <c r="S182" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S182" s="3"/>
       <c r="T182" s="3"/>
       <c r="U182" s="3"/>
       <c r="V182" s="3"/>
@@ -16279,7 +16277,7 @@
         <v>181</v>
       </c>
       <c r="B183" s="7">
-        <v>2026040057</v>
+        <v>2026040056</v>
       </c>
       <c r="C183" s="7">
         <v>1</v>
@@ -16318,7 +16316,7 @@
         <v>560</v>
       </c>
       <c r="O183" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P183" s="7"/>
       <c r="Q183" s="7">
@@ -16327,7 +16325,9 @@
       <c r="R183" s="7">
         <v>361051</v>
       </c>
-      <c r="S183" s="7"/>
+      <c r="S183" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T183" s="7"/>
       <c r="U183" s="7"/>
       <c r="V183" s="7"/>
@@ -16419,7 +16419,7 @@
         <v>183</v>
       </c>
       <c r="B185" s="7">
-        <v>2026040537</v>
+        <v>2026040538</v>
       </c>
       <c r="C185" s="7">
         <v>1</v>
@@ -16458,7 +16458,7 @@
         <v>585</v>
       </c>
       <c r="O185" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P185" s="7"/>
       <c r="Q185" s="7">
@@ -16467,9 +16467,7 @@
       <c r="R185" s="7">
         <v>29387</v>
       </c>
-      <c r="S185" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S185" s="7"/>
       <c r="T185" s="7"/>
       <c r="U185" s="7"/>
       <c r="V185" s="7"/>
@@ -16479,15 +16477,19 @@
       <c r="Z185" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="AA185" s="7"/>
-      <c r="AB185" s="7"/>
+      <c r="AA185" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB185" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="186" spans="1:28">
       <c r="A186" s="3">
         <v>184</v>
       </c>
       <c r="B186" s="3">
-        <v>2026040538</v>
+        <v>2026040537</v>
       </c>
       <c r="C186" s="3">
         <v>1</v>
@@ -16526,7 +16528,7 @@
         <v>585</v>
       </c>
       <c r="O186" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P186" s="3"/>
       <c r="Q186" s="3">
@@ -16535,7 +16537,9 @@
       <c r="R186" s="3">
         <v>29387</v>
       </c>
-      <c r="S186" s="3"/>
+      <c r="S186" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
       <c r="V186" s="3"/>
@@ -16545,9 +16549,7 @@
       <c r="Z186" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="AA186" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA186" s="3"/>
       <c r="AB186" s="3"/>
     </row>
     <row r="187" spans="1:28">
@@ -18508,7 +18510,7 @@
         <v>185</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H216" s="3" t="s">
         <v>661</v>
@@ -22921,7 +22923,7 @@
         <v>280</v>
       </c>
       <c r="B282" s="3">
-        <v>2026040916</v>
+        <v>2026040917</v>
       </c>
       <c r="C282" s="3">
         <v>1</v>
@@ -22960,7 +22962,7 @@
         <v>824</v>
       </c>
       <c r="O282" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P282" s="3"/>
       <c r="Q282" s="3">
@@ -22969,17 +22971,13 @@
       <c r="R282" s="3">
         <v>22500</v>
       </c>
-      <c r="S282" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S282" s="3"/>
       <c r="T282" s="3"/>
       <c r="U282" s="3"/>
       <c r="V282" s="3"/>
       <c r="W282" s="3"/>
       <c r="X282" s="3"/>
-      <c r="Y282" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y282" s="3"/>
       <c r="Z282" s="6" t="s">
         <v>801</v>
       </c>
@@ -22995,7 +22993,7 @@
         <v>281</v>
       </c>
       <c r="B283" s="7">
-        <v>2026040917</v>
+        <v>2026040916</v>
       </c>
       <c r="C283" s="7">
         <v>1</v>
@@ -23034,7 +23032,7 @@
         <v>824</v>
       </c>
       <c r="O283" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P283" s="7"/>
       <c r="Q283" s="7">
@@ -23043,13 +23041,17 @@
       <c r="R283" s="7">
         <v>22500</v>
       </c>
-      <c r="S283" s="7"/>
+      <c r="S283" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T283" s="7"/>
       <c r="U283" s="7"/>
       <c r="V283" s="7"/>
       <c r="W283" s="7"/>
       <c r="X283" s="7"/>
-      <c r="Y283" s="7"/>
+      <c r="Y283" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z283" s="8" t="s">
         <v>801</v>
       </c>
@@ -24317,7 +24319,7 @@
         <v>300</v>
       </c>
       <c r="B302" s="3">
-        <v>2026043305</v>
+        <v>2026043306</v>
       </c>
       <c r="C302" s="3">
         <v>1</v>
@@ -24356,16 +24358,14 @@
         <v>860</v>
       </c>
       <c r="O302" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P302" s="3"/>
       <c r="Q302" s="3"/>
       <c r="R302" s="3">
         <v>786</v>
       </c>
-      <c r="S302" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S302" s="3"/>
       <c r="T302" s="3"/>
       <c r="U302" s="3"/>
       <c r="V302" s="3"/>
@@ -24387,7 +24387,7 @@
         <v>301</v>
       </c>
       <c r="B303" s="7">
-        <v>2026043306</v>
+        <v>2026043305</v>
       </c>
       <c r="C303" s="7">
         <v>1</v>
@@ -24426,14 +24426,16 @@
         <v>860</v>
       </c>
       <c r="O303" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P303" s="7"/>
       <c r="Q303" s="7"/>
       <c r="R303" s="7">
         <v>786</v>
       </c>
-      <c r="S303" s="7"/>
+      <c r="S303" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T303" s="7"/>
       <c r="U303" s="7"/>
       <c r="V303" s="7"/>
@@ -24857,7 +24859,7 @@
         <v>308</v>
       </c>
       <c r="B310" s="3">
-        <v>2026040831</v>
+        <v>2026040832</v>
       </c>
       <c r="C310" s="3">
         <v>1</v>
@@ -24896,16 +24898,14 @@
         <v>873</v>
       </c>
       <c r="O310" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P310" s="3"/>
       <c r="Q310" s="3"/>
       <c r="R310" s="3">
         <v>86361</v>
       </c>
-      <c r="S310" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S310" s="3"/>
       <c r="T310" s="3"/>
       <c r="U310" s="3"/>
       <c r="V310" s="3"/>
@@ -24927,7 +24927,7 @@
         <v>309</v>
       </c>
       <c r="B311" s="7">
-        <v>2026040832</v>
+        <v>2026040831</v>
       </c>
       <c r="C311" s="7">
         <v>1</v>
@@ -24966,14 +24966,16 @@
         <v>873</v>
       </c>
       <c r="O311" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P311" s="7"/>
       <c r="Q311" s="7"/>
       <c r="R311" s="7">
         <v>86361</v>
       </c>
-      <c r="S311" s="7"/>
+      <c r="S311" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T311" s="7"/>
       <c r="U311" s="7"/>
       <c r="V311" s="7"/>
@@ -27109,7 +27111,7 @@
         <v>341</v>
       </c>
       <c r="B343" s="7">
-        <v>2026042895</v>
+        <v>2026042896</v>
       </c>
       <c r="C343" s="7">
         <v>1</v>
@@ -27148,16 +27150,14 @@
         <v>911</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P343" s="7"/>
       <c r="Q343" s="7"/>
       <c r="R343" s="7">
         <v>6975</v>
       </c>
-      <c r="S343" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S343" s="7"/>
       <c r="T343" s="7"/>
       <c r="U343" s="7"/>
       <c r="V343" s="7"/>
@@ -27167,15 +27167,19 @@
       <c r="Z343" s="8" t="s">
         <v>801</v>
       </c>
-      <c r="AA343" s="7"/>
-      <c r="AB343" s="7"/>
+      <c r="AA343" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB343" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="344" spans="1:28">
       <c r="A344" s="3">
         <v>342</v>
       </c>
       <c r="B344" s="3">
-        <v>2026042896</v>
+        <v>2026042895</v>
       </c>
       <c r="C344" s="3">
         <v>1</v>
@@ -27214,14 +27218,16 @@
         <v>911</v>
       </c>
       <c r="O344" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P344" s="3"/>
       <c r="Q344" s="3"/>
       <c r="R344" s="3">
         <v>6975</v>
       </c>
-      <c r="S344" s="3"/>
+      <c r="S344" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T344" s="3"/>
       <c r="U344" s="3"/>
       <c r="V344" s="3"/>
@@ -27231,9 +27237,7 @@
       <c r="Z344" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="AA344" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA344" s="3"/>
       <c r="AB344" s="3"/>
     </row>
     <row r="345" spans="1:28">
@@ -27509,7 +27513,7 @@
         <v>347</v>
       </c>
       <c r="B349" s="7">
-        <v>2026043917</v>
+        <v>2026043911</v>
       </c>
       <c r="C349" s="7">
         <v>1</v>
@@ -27575,7 +27579,7 @@
         <v>348</v>
       </c>
       <c r="B350" s="3">
-        <v>2026043918</v>
+        <v>2026043912</v>
       </c>
       <c r="C350" s="3">
         <v>1</v>
@@ -27641,7 +27645,7 @@
         <v>349</v>
       </c>
       <c r="B351" s="7">
-        <v>2026043911</v>
+        <v>2026043917</v>
       </c>
       <c r="C351" s="7">
         <v>1</v>
@@ -27707,7 +27711,7 @@
         <v>350</v>
       </c>
       <c r="B352" s="3">
-        <v>2026043912</v>
+        <v>2026043918</v>
       </c>
       <c r="C352" s="3">
         <v>1</v>
@@ -30395,7 +30399,7 @@
         <v>390</v>
       </c>
       <c r="B392" s="3">
-        <v>2026041281</v>
+        <v>2026041280</v>
       </c>
       <c r="C392" s="3">
         <v>1</v>
@@ -30434,14 +30438,16 @@
         <v>931</v>
       </c>
       <c r="O392" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P392" s="3"/>
       <c r="Q392" s="3"/>
       <c r="R392" s="3">
         <v>359</v>
       </c>
-      <c r="S392" s="3"/>
+      <c r="S392" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T392" s="3"/>
       <c r="U392" s="3"/>
       <c r="V392" s="3"/>
@@ -30451,19 +30457,15 @@
       <c r="Z392" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="AA392" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB392" s="3">
-        <v>1</v>
-      </c>
+      <c r="AA392" s="3"/>
+      <c r="AB392" s="3"/>
     </row>
     <row r="393" spans="1:28">
       <c r="A393" s="7">
         <v>391</v>
       </c>
       <c r="B393" s="7">
-        <v>2026041280</v>
+        <v>2026041281</v>
       </c>
       <c r="C393" s="7">
         <v>1</v>
@@ -30502,16 +30504,14 @@
         <v>931</v>
       </c>
       <c r="O393" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P393" s="7"/>
       <c r="Q393" s="7"/>
       <c r="R393" s="7">
         <v>359</v>
       </c>
-      <c r="S393" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S393" s="7"/>
       <c r="T393" s="7"/>
       <c r="U393" s="7"/>
       <c r="V393" s="7"/>
@@ -30521,7 +30521,9 @@
       <c r="Z393" s="8" t="s">
         <v>801</v>
       </c>
-      <c r="AA393" s="7"/>
+      <c r="AA393" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB393" s="7"/>
     </row>
     <row r="394" spans="1:28">
@@ -30943,7 +30945,7 @@
         <v>398</v>
       </c>
       <c r="B400" s="3">
-        <v>2026043307</v>
+        <v>2026043308</v>
       </c>
       <c r="C400" s="3">
         <v>1</v>
@@ -30982,16 +30984,14 @@
         <v>860</v>
       </c>
       <c r="O400" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P400" s="3"/>
       <c r="Q400" s="3"/>
       <c r="R400" s="3">
         <v>159550</v>
       </c>
-      <c r="S400" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S400" s="3"/>
       <c r="T400" s="3"/>
       <c r="U400" s="3"/>
       <c r="V400" s="3"/>
@@ -31013,7 +31013,7 @@
         <v>399</v>
       </c>
       <c r="B401" s="7">
-        <v>2026043308</v>
+        <v>2026043307</v>
       </c>
       <c r="C401" s="7">
         <v>1</v>
@@ -31052,14 +31052,16 @@
         <v>860</v>
       </c>
       <c r="O401" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P401" s="7"/>
       <c r="Q401" s="7"/>
       <c r="R401" s="7">
         <v>159550</v>
       </c>
-      <c r="S401" s="7"/>
+      <c r="S401" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T401" s="7"/>
       <c r="U401" s="7"/>
       <c r="V401" s="7"/>
@@ -33466,7 +33468,7 @@
         <v>1062</v>
       </c>
       <c r="G437" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H437" s="7" t="s">
         <v>60</v>
@@ -34327,7 +34329,7 @@
         <v>448</v>
       </c>
       <c r="B450" s="3">
-        <v>2026042725</v>
+        <v>2026042726</v>
       </c>
       <c r="C450" s="3">
         <v>1</v>
@@ -34366,16 +34368,14 @@
         <v>1096</v>
       </c>
       <c r="O450" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P450" s="3"/>
       <c r="Q450" s="3"/>
       <c r="R450" s="3">
         <v>9617</v>
       </c>
-      <c r="S450" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S450" s="3"/>
       <c r="T450" s="3"/>
       <c r="U450" s="3"/>
       <c r="V450" s="3"/>
@@ -34385,15 +34385,19 @@
       <c r="Z450" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="AA450" s="3"/>
-      <c r="AB450" s="3"/>
+      <c r="AA450" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB450" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="451" spans="1:28">
       <c r="A451" s="7">
         <v>449</v>
       </c>
       <c r="B451" s="7">
-        <v>2026042726</v>
+        <v>2026042725</v>
       </c>
       <c r="C451" s="7">
         <v>1</v>
@@ -34432,14 +34436,16 @@
         <v>1096</v>
       </c>
       <c r="O451" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P451" s="7"/>
       <c r="Q451" s="7"/>
       <c r="R451" s="7">
         <v>9617</v>
       </c>
-      <c r="S451" s="7"/>
+      <c r="S451" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T451" s="7"/>
       <c r="U451" s="7"/>
       <c r="V451" s="7"/>
@@ -34449,9 +34455,7 @@
       <c r="Z451" s="8" t="s">
         <v>801</v>
       </c>
-      <c r="AA451" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA451" s="7"/>
       <c r="AB451" s="7"/>
     </row>
     <row r="452" spans="1:28">
@@ -35415,7 +35419,7 @@
         <v>464</v>
       </c>
       <c r="B466" s="3">
-        <v>2026041055</v>
+        <v>2026040568</v>
       </c>
       <c r="C466" s="3">
         <v>1</v>
@@ -35433,33 +35437,35 @@
         <v>130</v>
       </c>
       <c r="H466" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="I466" s="3" t="s">
         <v>1134</v>
       </c>
-      <c r="I466" s="3" t="s">
-        <v>1135</v>
-      </c>
-      <c r="J466" s="3"/>
-      <c r="K466" s="3"/>
+      <c r="J466" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="K466" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="L466" s="6" t="s">
         <v>290</v>
       </c>
       <c r="M466" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="N466" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="N466" s="6" t="s">
-        <v>1137</v>
-      </c>
       <c r="O466" s="3" t="s">
-        <v>39</v>
+        <v>230</v>
       </c>
       <c r="P466" s="3"/>
       <c r="Q466" s="3"/>
       <c r="R466" s="3">
         <v>0</v>
       </c>
-      <c r="S466" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S466" s="3"/>
       <c r="T466" s="3"/>
       <c r="U466" s="3"/>
       <c r="V466" s="3"/>
@@ -35467,7 +35473,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
       <c r="Z466" s="6" t="s">
-        <v>296</v>
+        <v>1137</v>
       </c>
       <c r="AA466" s="3" t="s">
         <v>40</v>
@@ -35481,7 +35487,7 @@
         <v>465</v>
       </c>
       <c r="B467" s="7">
-        <v>2026040568</v>
+        <v>2026041055</v>
       </c>
       <c r="C467" s="7">
         <v>1</v>
@@ -35499,35 +35505,33 @@
         <v>130</v>
       </c>
       <c r="H467" s="7" t="s">
-        <v>557</v>
+        <v>1138</v>
       </c>
       <c r="I467" s="7" t="s">
-        <v>1135</v>
-      </c>
-      <c r="J467" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="K467" s="7" t="s">
-        <v>289</v>
-      </c>
+        <v>1134</v>
+      </c>
+      <c r="J467" s="7"/>
+      <c r="K467" s="7"/>
       <c r="L467" s="8" t="s">
         <v>290</v>
       </c>
       <c r="M467" s="8" t="s">
+        <v>1135</v>
+      </c>
+      <c r="N467" s="8" t="s">
         <v>1136</v>
       </c>
-      <c r="N467" s="8" t="s">
-        <v>1137</v>
-      </c>
       <c r="O467" s="7" t="s">
-        <v>230</v>
+        <v>39</v>
       </c>
       <c r="P467" s="7"/>
       <c r="Q467" s="7"/>
       <c r="R467" s="7">
         <v>0</v>
       </c>
-      <c r="S467" s="7"/>
+      <c r="S467" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T467" s="7"/>
       <c r="U467" s="7"/>
       <c r="V467" s="7"/>
@@ -35535,7 +35539,7 @@
       <c r="X467" s="7"/>
       <c r="Y467" s="7"/>
       <c r="Z467" s="8" t="s">
-        <v>1138</v>
+        <v>296</v>
       </c>
       <c r="AA467" s="7" t="s">
         <v>40</v>
@@ -35568,7 +35572,7 @@
         <v>1139</v>
       </c>
       <c r="I468" s="3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="J468" s="3" t="s">
         <v>288</v>
@@ -35580,10 +35584,10 @@
         <v>290</v>
       </c>
       <c r="M468" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="N468" s="6" t="s">
         <v>1136</v>
-      </c>
-      <c r="N468" s="6" t="s">
-        <v>1137</v>
       </c>
       <c r="O468" s="3" t="s">
         <v>230</v>
@@ -35641,7 +35645,7 @@
         <v>1141</v>
       </c>
       <c r="AB469" s="9">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
